--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -5064,7 +5064,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -11234,23 +11234,23 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
-        <v>8260000</v>
+        <v>6195000</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>27082</v>
+        <v>20311</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K163" s="5" t="n">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N163" s="3" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -14548,34 +14548,34 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
-        <v>8261000</v>
+        <v>6196000</v>
       </c>
       <c r="I214" s="5" t="n">
-        <v>26821</v>
+        <v>20117</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K214" s="5" t="n">
-        <v>6195750</v>
+        <v>6196000</v>
       </c>
       <c r="L214" s="5" t="n">
-        <v>20116</v>
+        <v>20117</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -17884,7 +17884,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -18132,7 +18132,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G341" s="3" t="inlineStr">
@@ -22756,7 +22756,7 @@
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -22818,7 +22818,7 @@
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
@@ -22942,7 +22942,7 @@
       </c>
       <c r="F345" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G345" s="3" t="inlineStr">
@@ -23004,7 +23004,7 @@
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G347" s="3" t="inlineStr">
@@ -23128,7 +23128,7 @@
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -25296,7 +25296,7 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
@@ -25358,7 +25358,7 @@
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
@@ -25420,7 +25420,7 @@
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
@@ -25482,7 +25482,7 @@
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr">
@@ -25544,7 +25544,7 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -25606,7 +25606,7 @@
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G385" s="3" t="inlineStr">
@@ -25668,7 +25668,7 @@
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
@@ -25730,7 +25730,7 @@
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr">
@@ -74210,7 +74210,7 @@
       </c>
       <c r="F1115" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1115" s="3" t="inlineStr">
@@ -74334,7 +74334,7 @@
       </c>
       <c r="F1117" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1117" s="3" t="inlineStr">
@@ -74396,7 +74396,7 @@
       </c>
       <c r="F1118" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1118" s="3" t="inlineStr">
@@ -74458,7 +74458,7 @@
       </c>
       <c r="F1119" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1119" s="3" t="inlineStr">
@@ -74520,7 +74520,7 @@
       </c>
       <c r="F1120" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G1120" s="3" t="inlineStr">
@@ -74823,17 +74823,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>138</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -75520,68 +75520,68 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
 $1277万
 $29,902/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $876万
 $28,614/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
 $876万
 $28,708/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
 $882万
 $28,905/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K10" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
 $903万
 $29,331/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L10" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
 $1371万
 $31,893/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M10" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1560万
 $32,437/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N10" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $939万
 $32,615/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -75774,20 +75774,20 @@
 (26年-09月-05日)</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
 $886万
 $28,753/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L12" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
 $1345万
 $31,279/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M12" s="24" t="inlineStr">
@@ -75885,36 +75885,36 @@
 (26年-09月-05日)</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
 $877万
 $28,461/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L13" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
 $1331万
 $30,963/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M13" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1514万
 $31,468/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N13" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $911万
 $31,628/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -76012,20 +76012,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M14" s="22" t="inlineStr">
+      <c r="M14" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1499万
 $31,173/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N14" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="N14" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $902万
 $31,323/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -76123,12 +76123,12 @@
 (26年-09月-05日)</t>
         </is>
       </c>
-      <c r="M15" s="22" t="inlineStr">
+      <c r="M15" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1484万
 $30,861/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N15" s="22" t="inlineStr">
@@ -76321,44 +76321,44 @@
 (26年-09月-05日)</t>
         </is>
       </c>
-      <c r="J17" s="23" t="inlineStr">
+      <c r="J17" s="24" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
-$826万
-$27,082/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K17" s="22" t="inlineStr">
+$620万
+$20,311/呎
+(26年-09月-09日)</t>
+        </is>
+      </c>
+      <c r="K17" s="23" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
 $847万
 $27,497/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L17" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L17" s="23" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
 $1285万
 $29,888/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M17" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M17" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1462万
 $30,395/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N17" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="N17" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $879万
 $30,517/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -76408,68 +76408,68 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
 $1190万
 $27,878/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $817万
 $26,693/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
 $817万
 $26,780/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
 $822万
 $26,941/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K18" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
 $843万
 $27,357/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L18" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
 $1279万
 $29,740/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M18" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M18" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1455万
 $30,241/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N18" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="N18" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $874万
 $30,337/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -76773,12 +76773,12 @@
 (26年-09月-06日)</t>
         </is>
       </c>
-      <c r="K21" s="23" t="inlineStr">
+      <c r="K21" s="24" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
-$826万
-$26,821/呎
-(在售)</t>
+$620万
+$20,117/呎
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="L21" s="24" t="inlineStr">
@@ -77185,68 +77185,68 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
 $1144万
 $26,785/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H25" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $785万
 $25,647/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
 $785万
 $25,731/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J25" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
 $790万
 $25,908/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K25" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="K25" s="23" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
 $810万
 $26,289/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L25" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L25" s="23" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
 $1228万
 $28,553/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M25" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M25" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1397万
 $29,035/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N25" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="N25" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $833万
 $28,917/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -77669,12 +77669,12 @@
 (26年-09月-05日)</t>
         </is>
       </c>
-      <c r="L29" s="22" t="inlineStr">
+      <c r="L29" s="23" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
 $1196万
 $27,805/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M29" s="24" t="inlineStr">
@@ -77780,12 +77780,12 @@
 (26年-09月-05日)</t>
         </is>
       </c>
-      <c r="L30" s="22" t="inlineStr">
+      <c r="L30" s="23" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
 $1190万
 $27,674/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M30" s="24" t="inlineStr">
@@ -77851,68 +77851,68 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="23" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
 $1105万
 $25,878/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H31" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $758万
 $24,784/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I31" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
 $758万
 $24,866/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J31" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
 $763万
 $25,013/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K31" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
 $782万
 $25,393/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L31" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L31" s="23" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
 $1183万
 $27,521/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M31" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M31" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1348万
 $28,029/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N31" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="N31" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $799万
 $27,757/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -78184,68 +78184,68 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
 $1089万
 $25,504/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H34" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $747万
 $24,399/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I34" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I34" s="23" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
 $747万
 $24,479/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J34" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
 $752万
 $24,646/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K34" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
 $771万
 $25,032/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L34" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="L34" s="23" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
 $1166万
 $27,116/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M34" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="M34" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1333万
 $27,719/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="N34" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="N34" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
 $787万
 $27,340/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -81697,12 +81697,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -84822,36 +84822,36 @@
       </c>
       <c r="E32" s="25" t="inlineStr"/>
       <c r="F32" s="25" t="inlineStr"/>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>F | 307呎 (1房)
 $763万
 $24,840/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H32" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
 $763万
 $24,922/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I32" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
         <is>
           <t>H | 306呎 (1房)
 $773万
 $25,271/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J32" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
         <is>
           <t>J | 308呎 (1房)
 $773万
 $25,107/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="K32" s="24" t="inlineStr">
@@ -84862,12 +84862,12 @@
 (26年-08月-22日)</t>
         </is>
       </c>
-      <c r="L32" s="22" t="inlineStr">
+      <c r="L32" s="23" t="inlineStr">
         <is>
           <t>L | 307呎 (1房)
 $757万
 $24,668/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="M32" s="24" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -8044,34 +8044,34 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
-        <v>12389000</v>
+        <v>9292000</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>29014</v>
+        <v>21761</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="5" t="n">
-        <v>9291750</v>
+        <v>9292000</v>
       </c>
       <c r="L114" s="5" t="n">
         <v>21761</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
@@ -11172,34 +11172,34 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
-        <v>8469000</v>
+        <v>6352000</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>27497</v>
+        <v>20623</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="5" t="n">
-        <v>6351750</v>
+        <v>6352000</v>
       </c>
       <c r="L162" s="5" t="n">
         <v>20623</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N162" s="3" t="inlineStr">
@@ -11894,34 +11894,34 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
-        <v>14546000</v>
+        <v>10910000</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>30241</v>
+        <v>22682</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K173" s="5" t="n">
-        <v>10909500</v>
+        <v>10910000</v>
       </c>
       <c r="L173" s="5" t="n">
-        <v>22681</v>
+        <v>22682</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr">
@@ -12018,34 +12018,34 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
-        <v>8426000</v>
+        <v>6320000</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>27357</v>
+        <v>20519</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K175" s="5" t="n">
-        <v>6319500</v>
+        <v>6320000</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>20518</v>
+        <v>20519</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N175" s="3" t="inlineStr">
@@ -12080,34 +12080,34 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
-        <v>8217000</v>
+        <v>6163000</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>26941</v>
+        <v>20207</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K176" s="5" t="n">
-        <v>6162750</v>
+        <v>6163000</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>20206</v>
+        <v>20207</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N176" s="3" t="inlineStr">
@@ -12142,23 +12142,23 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
-        <v>8168000</v>
+        <v>6126000</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>26780</v>
+        <v>20085</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K177" s="5" t="n">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
@@ -12204,23 +12204,23 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
-        <v>8168000</v>
+        <v>6126000</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>26693</v>
+        <v>20020</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K178" s="5" t="n">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -12266,23 +12266,23 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
-        <v>11904000</v>
+        <v>8928000</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>27878</v>
+        <v>20909</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K179" s="5" t="n">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N179" s="3" t="inlineStr">
@@ -17884,34 +17884,34 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
-        <v>8097000</v>
+        <v>6073000</v>
       </c>
       <c r="I266" s="5" t="n">
-        <v>26289</v>
+        <v>19718</v>
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K266" s="5" t="n">
-        <v>6072750</v>
+        <v>6073000</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>19717</v>
+        <v>19718</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
@@ -17946,34 +17946,34 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
-        <v>7902000</v>
+        <v>5927000</v>
       </c>
       <c r="I267" s="5" t="n">
-        <v>25908</v>
+        <v>19433</v>
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K267" s="5" t="n">
-        <v>5926500</v>
+        <v>5927000</v>
       </c>
       <c r="L267" s="5" t="n">
-        <v>19431</v>
+        <v>19433</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
@@ -18008,23 +18008,23 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
-        <v>7848000</v>
+        <v>5886000</v>
       </c>
       <c r="I268" s="5" t="n">
-        <v>25731</v>
+        <v>19298</v>
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K268" s="5" t="n">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
@@ -18070,23 +18070,23 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
-        <v>7848000</v>
+        <v>5886000</v>
       </c>
       <c r="I269" s="5" t="n">
-        <v>25647</v>
+        <v>19235</v>
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K269" s="5" t="n">
@@ -18097,7 +18097,7 @@
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
@@ -18132,34 +18132,34 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
-        <v>11437000</v>
+        <v>8578000</v>
       </c>
       <c r="I270" s="5" t="n">
-        <v>26785</v>
+        <v>20089</v>
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K270" s="5" t="n">
-        <v>8577750</v>
+        <v>8578000</v>
       </c>
       <c r="L270" s="5" t="n">
-        <v>20088</v>
+        <v>20089</v>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
@@ -18474,38 +18474,30 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H275" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I275" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H275" s="5" t="n">
+        <v>18068000</v>
+      </c>
+      <c r="I275" s="5" t="n">
+        <v>23435</v>
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K275" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L275" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K275" s="5" t="n">
+        <v>18068000</v>
+      </c>
+      <c r="L275" s="5" t="n">
+        <v>23435</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
@@ -18514,7 +18506,7 @@
       </c>
       <c r="N275" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19172,38 +19164,30 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H286" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I286" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="H286" s="5" t="n">
+        <v>10508000</v>
+      </c>
+      <c r="I286" s="5" t="n">
+        <v>21100</v>
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K286" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L286" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K286" s="5" t="n">
+        <v>10508000</v>
+      </c>
+      <c r="L286" s="5" t="n">
+        <v>21100</v>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
@@ -19212,7 +19196,7 @@
       </c>
       <c r="N286" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21538,30 +21522,38 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="H323" s="5" t="n">
-        <v>9456000</v>
-      </c>
-      <c r="I323" s="5" t="n">
-        <v>21638</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H323" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I323" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K323" s="5" t="n">
-        <v>9456000</v>
-      </c>
-      <c r="L323" s="5" t="n">
-        <v>21638</v>
+      <c r="K323" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L323" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
@@ -21570,7 +21562,7 @@
       </c>
       <c r="N323" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -22117,7 +22109,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -22624,38 +22616,30 @@
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H340" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I340" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H340" s="5" t="n">
+        <v>17388000</v>
+      </c>
+      <c r="I340" s="5" t="n">
+        <v>22553</v>
       </c>
       <c r="J340" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K340" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L340" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K340" s="5" t="n">
+        <v>17388000</v>
+      </c>
+      <c r="L340" s="5" t="n">
+        <v>22553</v>
       </c>
       <c r="M340" s="3" t="inlineStr">
         <is>
@@ -22664,7 +22648,7 @@
       </c>
       <c r="N340" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -22880,34 +22864,34 @@
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
-        <v>7821000</v>
+        <v>5866000</v>
       </c>
       <c r="I344" s="5" t="n">
-        <v>25393</v>
+        <v>19045</v>
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K344" s="5" t="n">
-        <v>5865750</v>
+        <v>5866000</v>
       </c>
       <c r="L344" s="5" t="n">
         <v>19045</v>
       </c>
       <c r="M344" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N344" s="3" t="inlineStr">
@@ -22942,34 +22926,34 @@
       </c>
       <c r="F345" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
-        <v>7629000</v>
+        <v>5722000</v>
       </c>
       <c r="I345" s="5" t="n">
-        <v>25013</v>
+        <v>18761</v>
       </c>
       <c r="J345" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K345" s="5" t="n">
-        <v>5721750</v>
+        <v>5722000</v>
       </c>
       <c r="L345" s="5" t="n">
-        <v>18760</v>
+        <v>18761</v>
       </c>
       <c r="M345" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N345" s="3" t="inlineStr">
@@ -23004,23 +22988,23 @@
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
-        <v>7584000</v>
+        <v>5688000</v>
       </c>
       <c r="I346" s="5" t="n">
-        <v>24866</v>
+        <v>18649</v>
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K346" s="5" t="n">
@@ -23031,7 +23015,7 @@
       </c>
       <c r="M346" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N346" s="3" t="inlineStr">
@@ -23066,23 +23050,23 @@
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
-        <v>7584000</v>
+        <v>5688000</v>
       </c>
       <c r="I347" s="5" t="n">
-        <v>24784</v>
+        <v>18588</v>
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K347" s="5" t="n">
@@ -23093,7 +23077,7 @@
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N347" s="3" t="inlineStr">
@@ -23190,38 +23174,30 @@
       </c>
       <c r="F349" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H349" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I349" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="H349" s="5" t="n">
+        <v>9348000</v>
+      </c>
+      <c r="I349" s="5" t="n">
+        <v>21391</v>
       </c>
       <c r="J349" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K349" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L349" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K349" s="5" t="n">
+        <v>9348000</v>
+      </c>
+      <c r="L349" s="5" t="n">
+        <v>21391</v>
       </c>
       <c r="M349" s="3" t="inlineStr">
         <is>
@@ -23230,7 +23206,7 @@
       </c>
       <c r="N349" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23330,38 +23306,30 @@
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H351" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I351" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H351" s="5" t="n">
+        <v>10138000</v>
+      </c>
+      <c r="I351" s="5" t="n">
+        <v>20357</v>
       </c>
       <c r="J351" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K351" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L351" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K351" s="5" t="n">
+        <v>10138000</v>
+      </c>
+      <c r="L351" s="5" t="n">
+        <v>20357</v>
       </c>
       <c r="M351" s="3" t="inlineStr">
         <is>
@@ -23370,7 +23338,7 @@
       </c>
       <c r="N351" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23540,23 +23508,23 @@
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
-        <v>5955000</v>
+        <v>7940000</v>
       </c>
       <c r="I354" s="5" t="n">
-        <v>20677</v>
+        <v>27569</v>
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="K354" s="5" t="n">
@@ -23567,7 +23535,7 @@
       </c>
       <c r="M354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N354" s="3" t="inlineStr">
@@ -73285,7 +73253,7 @@
       </c>
       <c r="G1100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H1100" s="5" t="n">
@@ -74277,7 +74245,7 @@
       </c>
       <c r="G1116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H1116" s="5" t="n">
@@ -74711,7 +74679,7 @@
       </c>
       <c r="G1123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H1123" s="5" t="n">
@@ -74823,7 +74791,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>118</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -74833,7 +74801,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -75853,12 +75821,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="24" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
-$1239万
-$29,014/呎
-(在售)</t>
+$929万
+$21,761/呎
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -76329,12 +76297,12 @@
 (26年-09月-09日)</t>
         </is>
       </c>
-      <c r="K17" s="23" t="inlineStr">
+      <c r="K17" s="24" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
-$847万
-$27,497/呎
-(在售)</t>
+$635万
+$20,623/呎
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="L17" s="23" t="inlineStr">
@@ -76408,44 +76376,44 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G18" s="24" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
-$1190万
-$27,878/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H18" s="23" t="inlineStr">
+$893万
+$20,909/呎
+(26年-09月-13日)</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
-$817万
-$26,693/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
+$613万
+$20,020/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
-$817万
-$26,780/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J18" s="23" t="inlineStr">
+$613万
+$20,085/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="J18" s="24" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
-$822万
-$26,941/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K18" s="23" t="inlineStr">
+$616万
+$20,207/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="K18" s="24" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
-$843万
-$27,357/呎
-(在售)</t>
+$632万
+$20,519/呎
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="L18" s="23" t="inlineStr">
@@ -76456,12 +76424,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M18" s="23" t="inlineStr">
+      <c r="M18" s="24" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
-$1455万
-$30,241/呎
-(在售)</t>
+$1091万
+$22,682/呎
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="N18" s="23" t="inlineStr">
@@ -77145,12 +77113,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
-(在售)</t>
+$1807万
+$23,435/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -77185,44 +77153,44 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="G25" s="24" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
-$1144万
-$26,785/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H25" s="23" t="inlineStr">
+$858万
+$20,089/呎
+(26年-09月-13日)</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
-$785万
-$25,647/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I25" s="23" t="inlineStr">
+$589万
+$19,235/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
-$785万
-$25,731/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J25" s="23" t="inlineStr">
+$589万
+$19,298/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="J25" s="24" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
-$790万
-$25,908/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K25" s="23" t="inlineStr">
+$593万
+$19,433/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="K25" s="24" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
-$810万
-$26,289/呎
-(在售)</t>
+$607万
+$19,718/呎
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="L25" s="23" t="inlineStr">
@@ -77272,12 +77240,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-招标单位
--
-(在售)</t>
+$1051万
+$21,100/呎
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -77621,12 +77589,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F29" s="24" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
-$946万
-$21,638/呎
-(26年-09月-04日)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
@@ -77700,12 +77668,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
-(在售)</t>
+$1739万
+$22,553/呎
+(26年-09月-13日)</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -77769,7 +77737,7 @@
           <t>J | 305呎 (1房)
 $575万
 $18,852/呎
-(26年-09月-05日)</t>
+(26年-09月-13日)</t>
         </is>
       </c>
       <c r="K30" s="24" t="inlineStr">
@@ -77827,12 +77795,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-招标单位
--
-(在售)</t>
+$1014万
+$20,357/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -77843,12 +77811,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F31" s="23" t="inlineStr">
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
-招标单位
--
-(在售)</t>
+$935万
+$21,391/呎
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -77859,36 +77827,36 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H31" s="23" t="inlineStr">
+      <c r="H31" s="24" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
-$758万
-$24,784/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I31" s="23" t="inlineStr">
+$569万
+$18,588/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
-$758万
-$24,866/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
+$569万
+$18,649/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="J31" s="24" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
-$763万
-$25,013/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
+$572万
+$18,761/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
-$782万
-$25,393/呎
-(在售)</t>
+$587万
+$19,045/呎
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="L31" s="23" t="inlineStr">
@@ -78018,12 +77986,12 @@
 (26年-09月-07日)</t>
         </is>
       </c>
-      <c r="N32" s="24" t="inlineStr">
+      <c r="N32" s="23" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
-$596万
-$20,677/呎
-(26年-09月-05日)</t>
+$794万
+$27,569/呎
+(在售)</t>
         </is>
       </c>
     </row>
@@ -84579,7 +84547,7 @@
           <t>A | 613呎 (2房)
 $1338万
 $21,830/呎
-(26年-08月-25日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -84801,7 +84769,7 @@
           <t>A | 612呎 (2房)
 $1270万
 $20,748/呎
-(26年-08月-27日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -84859,7 +84827,7 @@
           <t>K | 426呎 (2房)
 $831万
 $19,502/呎
-(26年-08月-22日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="L32" s="23" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -21031,7 +21031,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -21786,38 +21786,30 @@
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H327" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I327" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H327" s="5" t="n">
+        <v>17498000</v>
+      </c>
+      <c r="I327" s="5" t="n">
+        <v>22695</v>
       </c>
       <c r="J327" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K327" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L327" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K327" s="5" t="n">
+        <v>17498000</v>
+      </c>
+      <c r="L327" s="5" t="n">
+        <v>22695</v>
       </c>
       <c r="M327" s="3" t="inlineStr">
         <is>
@@ -21826,7 +21818,7 @@
       </c>
       <c r="N327" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -22740,34 +22732,34 @@
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
-        <v>13482000</v>
+        <v>10112000</v>
       </c>
       <c r="I342" s="5" t="n">
-        <v>28029</v>
+        <v>21023</v>
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K342" s="5" t="n">
-        <v>10111500</v>
+        <v>10112000</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>21022</v>
+        <v>21023</v>
       </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N342" s="3" t="inlineStr">
@@ -23112,34 +23104,34 @@
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
-        <v>11050000</v>
+        <v>8288000</v>
       </c>
       <c r="I348" s="5" t="n">
-        <v>25878</v>
+        <v>19410</v>
       </c>
       <c r="J348" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K348" s="5" t="n">
-        <v>8287500</v>
+        <v>8288000</v>
       </c>
       <c r="L348" s="5" t="n">
-        <v>19409</v>
+        <v>19410</v>
       </c>
       <c r="M348" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N348" s="3" t="inlineStr">
@@ -25574,34 +25566,34 @@
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
-        <v>7466000</v>
+        <v>5600000</v>
       </c>
       <c r="I385" s="5" t="n">
-        <v>24479</v>
+        <v>18361</v>
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K385" s="5" t="n">
-        <v>5599500</v>
+        <v>5600000</v>
       </c>
       <c r="L385" s="5" t="n">
-        <v>18359</v>
+        <v>18361</v>
       </c>
       <c r="M385" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N385" s="3" t="inlineStr">
@@ -65045,7 +65037,7 @@
       </c>
       <c r="G968" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H968" s="5" t="n">
@@ -65169,7 +65161,7 @@
       </c>
       <c r="G970" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H970" s="5" t="n">
@@ -74121,7 +74113,7 @@
       </c>
       <c r="G1114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H1114" s="5" t="n">
@@ -74426,34 +74418,34 @@
       </c>
       <c r="F1119" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H1119" s="5" t="n">
-        <v>7626000</v>
+        <v>5720000</v>
       </c>
       <c r="I1119" s="5" t="n">
-        <v>24922</v>
+        <v>18693</v>
       </c>
       <c r="J1119" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1119" s="5" t="n">
-        <v>5719500</v>
+        <v>5720000</v>
       </c>
       <c r="L1119" s="5" t="n">
-        <v>18691</v>
+        <v>18693</v>
       </c>
       <c r="M1119" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1119" s="3" t="inlineStr">
@@ -74488,34 +74480,34 @@
       </c>
       <c r="F1120" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H1120" s="5" t="n">
-        <v>7626000</v>
+        <v>5720000</v>
       </c>
       <c r="I1120" s="5" t="n">
-        <v>24840</v>
+        <v>18632</v>
       </c>
       <c r="J1120" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1120" s="5" t="n">
-        <v>5719500</v>
+        <v>5720000</v>
       </c>
       <c r="L1120" s="5" t="n">
-        <v>18630</v>
+        <v>18632</v>
       </c>
       <c r="M1120" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1120" s="3" t="inlineStr">
@@ -74791,7 +74783,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -74801,7 +74793,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>132</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -77557,12 +77549,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
-(在售)</t>
+$1750万
+$22,695/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -77658,7 +77650,7 @@
           <t>N | 288呎 (1房)
 $606万
 $21,059/呎
-(26年-09月-05日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
     </row>
@@ -77819,12 +77811,12 @@
 (26年-09月-10日)</t>
         </is>
       </c>
-      <c r="G31" s="23" t="inlineStr">
+      <c r="G31" s="24" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
-$1105万
-$25,878/呎
-(在售)</t>
+$829万
+$19,410/呎
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
@@ -77867,12 +77859,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M31" s="23" t="inlineStr">
+      <c r="M31" s="24" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
-$1348万
-$28,029/呎
-(在售)</t>
+$1011万
+$21,023/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
@@ -78168,12 +78160,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I34" s="23" t="inlineStr">
+      <c r="I34" s="24" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
-$747万
-$24,479/呎
-(在售)</t>
+$560万
+$18,361/呎
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
@@ -81665,7 +81657,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -81675,7 +81667,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -83437,7 +83429,7 @@
           <t>A | 613呎 (2房)
 $1450万
 $23,651/呎
-(26年-08月-25日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -83453,7 +83445,7 @@
           <t>C | 548呎 (2房)
 $1299万
 $23,701/呎
-(26年-08月-19日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -84790,20 +84782,20 @@
       </c>
       <c r="E32" s="25" t="inlineStr"/>
       <c r="F32" s="25" t="inlineStr"/>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="G32" s="24" t="inlineStr">
         <is>
           <t>F | 307呎 (1房)
-$763万
-$24,840/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H32" s="23" t="inlineStr">
+$572万
+$18,632/呎
+(26年-09月-17日)</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
-$763万
-$24,922/呎
-(在售)</t>
+$572万
+$18,693/呎
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
@@ -84843,7 +84835,7 @@
           <t>M | 668呎 (3房)
 $1772万
 $26,527/呎
-(26年-08月-22日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="N32" s="25" t="inlineStr"/>

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -7141,7 +7141,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7796,34 +7796,34 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
-        <v>8766000</v>
+        <v>6575000</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>28461</v>
+        <v>21347</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="5" t="n">
-        <v>6574500</v>
+        <v>6575000</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>21346</v>
+        <v>21347</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -11048,23 +11048,23 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
-        <v>14620000</v>
+        <v>10965000</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>30395</v>
+        <v>22796</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14429,7 +14429,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -17698,23 +17698,23 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
-        <v>8328000</v>
+        <v>6246000</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>28917</v>
+        <v>21688</v>
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K263" s="5" t="n">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
@@ -17760,34 +17760,34 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
-        <v>13966000</v>
+        <v>10475000</v>
       </c>
       <c r="I264" s="5" t="n">
-        <v>29035</v>
+        <v>21778</v>
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K264" s="5" t="n">
-        <v>10474500</v>
+        <v>10475000</v>
       </c>
       <c r="L264" s="5" t="n">
-        <v>21777</v>
+        <v>21778</v>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N264" s="3" t="inlineStr">
@@ -18660,34 +18660,34 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
-        <v>12217000</v>
+        <v>9163000</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>28412</v>
+        <v>21309</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K278" s="5" t="n">
-        <v>9162750</v>
+        <v>9163000</v>
       </c>
       <c r="L278" s="5" t="n">
         <v>21309</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N278" s="3" t="inlineStr">
@@ -19363,7 +19363,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -19797,7 +19797,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -21279,7 +21279,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -21403,7 +21403,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -22225,7 +22225,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -23691,7 +23691,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -23815,7 +23815,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -23939,7 +23939,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -25504,34 +25504,34 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
-        <v>7517000</v>
+        <v>5638000</v>
       </c>
       <c r="I384" s="5" t="n">
-        <v>24646</v>
+        <v>18485</v>
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K384" s="5" t="n">
-        <v>5637750</v>
+        <v>5638000</v>
       </c>
       <c r="L384" s="5" t="n">
-        <v>18484</v>
+        <v>18485</v>
       </c>
       <c r="M384" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N384" s="3" t="inlineStr">
@@ -25628,34 +25628,34 @@
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
-        <v>7466000</v>
+        <v>5600000</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>24399</v>
+        <v>18301</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K386" s="5" t="n">
-        <v>5599500</v>
+        <v>5600000</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>18299</v>
+        <v>18301</v>
       </c>
       <c r="M386" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N386" s="3" t="inlineStr">
@@ -25752,38 +25752,30 @@
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H388" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I388" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H388" s="5" t="n">
+        <v>9178000</v>
+      </c>
+      <c r="I388" s="5" t="n">
+        <v>21002</v>
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K388" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L388" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K388" s="5" t="n">
+        <v>9178000</v>
+      </c>
+      <c r="L388" s="5" t="n">
+        <v>21002</v>
       </c>
       <c r="M388" s="3" t="inlineStr">
         <is>
@@ -25792,7 +25784,7 @@
       </c>
       <c r="N388" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -25892,38 +25884,30 @@
       </c>
       <c r="F390" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H390" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I390" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H390" s="5" t="n">
+        <v>9968000</v>
+      </c>
+      <c r="I390" s="5" t="n">
+        <v>20016</v>
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K390" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L390" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K390" s="5" t="n">
+        <v>9968000</v>
+      </c>
+      <c r="L390" s="5" t="n">
+        <v>20016</v>
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
@@ -25932,7 +25916,7 @@
       </c>
       <c r="N390" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -64905,7 +64889,7 @@
       </c>
       <c r="G966" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H966" s="5" t="n">
@@ -74294,34 +74278,34 @@
       </c>
       <c r="F1117" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H1117" s="5" t="n">
-        <v>7733000</v>
+        <v>5800000</v>
       </c>
       <c r="I1117" s="5" t="n">
-        <v>25107</v>
+        <v>18831</v>
       </c>
       <c r="J1117" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1117" s="5" t="n">
-        <v>5799750</v>
+        <v>5800000</v>
       </c>
       <c r="L1117" s="5" t="n">
-        <v>18830</v>
+        <v>18831</v>
       </c>
       <c r="M1117" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1117" s="3" t="inlineStr">
@@ -74783,7 +74767,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -74793,7 +74777,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>141</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -75715,7 +75699,7 @@
           <t>G | 306呎 (1房)
 $644万
 $21,042/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
@@ -75834,7 +75818,7 @@
           <t>H | 305呎 (1房)
 $637万
 $20,895/呎
-(26年-09月-05日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="J13" s="24" t="inlineStr">
@@ -75845,12 +75829,12 @@
 (26年-09月-05日)</t>
         </is>
       </c>
-      <c r="K13" s="23" t="inlineStr">
+      <c r="K13" s="24" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
-$877万
-$28,461/呎
-(在售)</t>
+$658万
+$21,347/呎
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="L13" s="23" t="inlineStr">
@@ -75953,7 +75937,7 @@
           <t>J | 305呎 (1房)
 $635万
 $20,826/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="K14" s="24" t="inlineStr">
@@ -75961,7 +75945,7 @@
           <t>K | 308呎 (1房)
 $651万
 $21,140/呎
-(26年-09月-06日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="L14" s="23" t="inlineStr">
@@ -76064,7 +76048,7 @@
           <t>J | 305呎 (1房)
 $629万
 $20,620/呎
-(26年-09月-05日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="K15" s="24" t="inlineStr">
@@ -76072,7 +76056,7 @@
           <t>K | 308呎 (1房)
 $645万
 $20,929/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="L15" s="24" t="inlineStr">
@@ -76175,7 +76159,7 @@
           <t>J | 305呎 (1房)
 $623万
 $20,416/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -76278,7 +76262,7 @@
           <t>H | 305呎 (1房)
 $616万
 $20,187/呎
-(26年-09月-05日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="J17" s="24" t="inlineStr">
@@ -76305,12 +76289,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M17" s="23" t="inlineStr">
+      <c r="M17" s="24" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
-$1462万
-$30,395/呎
-(在售)</t>
+$1096万
+$22,796/呎
+(26年-09月-20日)</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
@@ -76555,7 +76539,7 @@
           <t>A | 771呎 (3房)
 $1888万
 $24,488/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -76603,7 +76587,7 @@
           <t>G | 306呎 (1房)
 $606万
 $19,820/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="I20" s="24" t="inlineStr">
@@ -76698,7 +76682,7 @@
           <t>E | 437呎 (2房)
 $999万
 $22,856/呎
-(26年-09月-04日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
@@ -76714,7 +76698,7 @@
           <t>G | 306呎 (1房)
 $601万
 $19,627/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="I21" s="24" t="inlineStr">
@@ -76722,7 +76706,7 @@
           <t>H | 305呎 (1房)
 $601万
 $19,692/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="J21" s="24" t="inlineStr">
@@ -76754,7 +76738,7 @@
           <t>M | 481呎 (2房)
 $1069万
 $22,229/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="N21" s="24" t="inlineStr">
@@ -76762,7 +76746,7 @@
           <t>N | 288呎 (1房)
 $640万
 $22,215/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -76809,7 +76793,7 @@
           <t>E | 437呎 (2房)
 $1032万
 $23,627/呎
-(26年-09月-04日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
@@ -76841,7 +76825,7 @@
           <t>J | 305呎 (1房)
 $601万
 $19,715/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="K22" s="24" t="inlineStr">
@@ -76888,7 +76872,7 @@
           <t>A | 771呎 (3房)
 $1831万
 $23,746/呎
-(26年-09月-04日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -76952,7 +76936,7 @@
           <t>J | 305呎 (1房)
 $598万
 $19,623/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr">
@@ -77193,20 +77177,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M25" s="23" t="inlineStr">
+      <c r="M25" s="24" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
-$1397万
-$29,035/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="N25" s="23" t="inlineStr">
+$1048万
+$21,778/呎
+(26年-09月-18日)</t>
+        </is>
+      </c>
+      <c r="N25" s="24" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
-$833万
-$28,917/呎
-(在售)</t>
+$625万
+$21,688/呎
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -77296,12 +77280,12 @@
 (26年-09月-05日)</t>
         </is>
       </c>
-      <c r="L26" s="23" t="inlineStr">
+      <c r="L26" s="24" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
-$1222万
-$28,412/呎
-(在售)</t>
+$916万
+$21,309/呎
+(26年-09月-19日)</t>
         </is>
       </c>
       <c r="M26" s="24" t="inlineStr">
@@ -77372,7 +77356,7 @@
           <t>F | 427呎 (2房)
 $850万
 $19,902/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -77420,7 +77404,7 @@
           <t>M | 481呎 (2房)
 $1037万
 $21,555/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="N27" s="24" t="inlineStr">
@@ -77428,7 +77412,7 @@
           <t>N | 288呎 (1房)
 $617万
 $21,431/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
     </row>
@@ -77602,7 +77586,7 @@
           <t>G | 306呎 (1房)
 $574万
 $18,765/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="I29" s="24" t="inlineStr">
@@ -77618,7 +77602,7 @@
           <t>J | 305呎 (1房)
 $578万
 $18,951/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="K29" s="24" t="inlineStr">
@@ -77713,7 +77697,7 @@
           <t>G | 306呎 (1房)
 $572万
 $18,676/呎
-(26年-09月-05日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="I30" s="24" t="inlineStr">
@@ -77927,7 +77911,7 @@
           <t>F | 427呎 (2房)
 $824万
 $19,293/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -77943,7 +77927,7 @@
           <t>H | 305呎 (1房)
 $566万
 $18,541/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="J32" s="24" t="inlineStr">
@@ -77959,7 +77943,7 @@
           <t>K | 308呎 (1房)
 $584万
 $18,948/呎
-(26年-09月-05日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="L32" s="24" t="inlineStr">
@@ -78120,12 +78104,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-招标单位
--
-(在售)</t>
+$997万
+$20,016/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -78136,12 +78120,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
+      <c r="F34" s="24" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
-招标单位
--
-(在售)</t>
+$918万
+$21,002/呎
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
@@ -78152,12 +78136,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H34" s="23" t="inlineStr">
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
-$747万
-$24,399/呎
-(在售)</t>
+$560万
+$18,301/呎
+(26年-09月-20日)</t>
         </is>
       </c>
       <c r="I34" s="24" t="inlineStr">
@@ -78168,12 +78152,12 @@
 (26年-09月-15日)</t>
         </is>
       </c>
-      <c r="J34" s="23" t="inlineStr">
+      <c r="J34" s="24" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
-$752万
-$24,646/呎
-(在售)</t>
+$564万
+$18,485/呎
+(26年-09月-19日)</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
@@ -81657,7 +81641,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -81667,7 +81651,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -83461,7 +83445,7 @@
           <t>E | 499呎 (2房)
 $1149万
 $23,022/呎
-(26年-09月-02日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
@@ -84806,12 +84790,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J32" s="23" t="inlineStr">
+      <c r="J32" s="24" t="inlineStr">
         <is>
           <t>J | 308呎 (1房)
-$773万
-$25,107/呎
-(在售)</t>
+$580万
+$18,831/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="K32" s="24" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -15065,7 +15065,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -15308,34 +15308,34 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
-        <v>12470000</v>
+        <v>9353000</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>29000</v>
+        <v>21751</v>
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K226" s="5" t="n">
-        <v>9352500</v>
+        <v>9353000</v>
       </c>
       <c r="L226" s="5" t="n">
-        <v>21750</v>
+        <v>21751</v>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N226" s="3" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -16143,7 +16143,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -18603,7 +18603,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -18851,7 +18851,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -21667,7 +21667,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -21729,7 +21729,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -21853,7 +21853,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21915,7 +21915,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -22287,7 +22287,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -22349,7 +22349,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -23567,7 +23567,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -23629,7 +23629,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -23877,7 +23877,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -25442,34 +25442,34 @@
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
-        <v>7710000</v>
+        <v>5783000</v>
       </c>
       <c r="I383" s="5" t="n">
-        <v>25032</v>
+        <v>18776</v>
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K383" s="5" t="n">
-        <v>5782500</v>
+        <v>5783000</v>
       </c>
       <c r="L383" s="5" t="n">
-        <v>18774</v>
+        <v>18776</v>
       </c>
       <c r="M383" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N383" s="3" t="inlineStr">
@@ -64946,38 +64946,30 @@
       </c>
       <c r="F967" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G967" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H967" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I967" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H967" s="5" t="n">
+        <v>9888000</v>
+      </c>
+      <c r="I967" s="5" t="n">
+        <v>22889</v>
       </c>
       <c r="J967" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K967" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L967" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K967" s="5" t="n">
+        <v>9888000</v>
+      </c>
+      <c r="L967" s="5" t="n">
+        <v>22889</v>
       </c>
       <c r="M967" s="3" t="inlineStr">
         <is>
@@ -64986,7 +64978,7 @@
       </c>
       <c r="N967" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -69741,7 +69733,7 @@
       </c>
       <c r="G1044" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H1044" s="5" t="n">
@@ -74154,34 +74146,34 @@
       </c>
       <c r="F1115" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H1115" s="5" t="n">
-        <v>7573000</v>
+        <v>5680000</v>
       </c>
       <c r="I1115" s="5" t="n">
-        <v>24668</v>
+        <v>18502</v>
       </c>
       <c r="J1115" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1115" s="5" t="n">
-        <v>5679750</v>
+        <v>5680000</v>
       </c>
       <c r="L1115" s="5" t="n">
-        <v>18501</v>
+        <v>18502</v>
       </c>
       <c r="M1115" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1115" s="3" t="inlineStr">
@@ -74340,34 +74332,34 @@
       </c>
       <c r="F1118" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H1118" s="5" t="n">
-        <v>7733000</v>
+        <v>5800000</v>
       </c>
       <c r="I1118" s="5" t="n">
-        <v>25271</v>
+        <v>18954</v>
       </c>
       <c r="J1118" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1118" s="5" t="n">
-        <v>5799750</v>
+        <v>5800000</v>
       </c>
       <c r="L1118" s="5" t="n">
-        <v>18953</v>
+        <v>18954</v>
       </c>
       <c r="M1118" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1118" s="3" t="inlineStr">
@@ -74767,7 +74759,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -74777,7 +74769,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>143</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -75691,7 +75683,7 @@
           <t>F | 427呎 (2房)
 $938万
 $21,967/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -75715,7 +75707,7 @@
           <t>J | 305呎 (1房)
 $648万
 $21,246/呎
-(26年-09月-05日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr">
@@ -75739,7 +75731,7 @@
           <t>M | 481呎 (2房)
 $1147万
 $23,850/呎
-(26年-09月-05日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="N12" s="23" t="inlineStr">
@@ -75826,7 +75818,7 @@
           <t>J | 305呎 (1房)
 $642万
 $21,033/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="K13" s="24" t="inlineStr">
@@ -75913,7 +75905,7 @@
           <t>F | 427呎 (2房)
 $920万
 $21,546/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -75921,7 +75913,7 @@
           <t>G | 306呎 (1房)
 $631万
 $20,627/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="I14" s="24" t="inlineStr">
@@ -75929,7 +75921,7 @@
           <t>H | 305呎 (1房)
 $631万
 $20,695/呎
-(26年-09月-05日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="J14" s="24" t="inlineStr">
@@ -76024,7 +76016,7 @@
           <t>F | 427呎 (2房)
 $911万
 $21,330/呎
-(26年-09月-05日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -76040,7 +76032,7 @@
           <t>H | 305呎 (1房)
 $625万
 $20,485/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="J15" s="24" t="inlineStr">
@@ -76095,7 +76087,7 @@
           <t>A | 771呎 (3房)
 $1937万
 $25,121/呎
-(26年-09月-04日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -76246,7 +76238,7 @@
           <t>F | 427呎 (2房)
 $898万
 $21,021/呎
-(26年-09月-05日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -76254,7 +76246,7 @@
           <t>G | 306呎 (1房)
 $616万
 $20,121/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr">
@@ -76373,7 +76365,7 @@
           <t>H | 305呎 (1房)
 $613万
 $20,085/呎
-(26年-09月-10日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="J18" s="24" t="inlineStr">
@@ -76579,7 +76571,7 @@
           <t>F | 427呎 (2房)
 $884万
 $20,700/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -76595,7 +76587,7 @@
           <t>H | 305呎 (1房)
 $606万
 $19,885/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="J20" s="24" t="inlineStr">
@@ -76611,7 +76603,7 @@
           <t>K | 308呎 (1房)
 $626万
 $20,308/呎
-(26年-09月-05日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="L20" s="23" t="inlineStr">
@@ -76658,7 +76650,7 @@
           <t>B | 536呎 (2房)
 $1257万
 $23,455/呎
-(26年-09月-04日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -76690,7 +76682,7 @@
           <t>F | 427呎 (2房)
 $875万
 $20,492/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -76730,7 +76722,7 @@
           <t>L | 430呎 (2房)
 $940万
 $21,858/呎
-(26年-09月-05日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="M21" s="24" t="inlineStr">
@@ -76809,7 +76801,7 @@
           <t>G | 306呎 (1房)
 $598万
 $19,529/呎
-(26年-09月-05日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="I22" s="24" t="inlineStr">
@@ -76833,15 +76825,15 @@
           <t>K | 308呎 (1房)
 $616万
 $20,016/呎
-(26年-09月-05日)</t>
-        </is>
-      </c>
-      <c r="L22" s="23" t="inlineStr">
+(26年-09月-22日)</t>
+        </is>
+      </c>
+      <c r="L22" s="24" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
-$1247万
-$29,000/呎
-(在售)</t>
+$935万
+$21,751/呎
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="M22" s="24" t="inlineStr">
@@ -76849,7 +76841,7 @@
           <t>M | 481呎 (2房)
 $1064万
 $22,116/呎
-(26年-09月-05日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="N22" s="23" t="inlineStr">
@@ -76912,7 +76904,7 @@
           <t>F | 427呎 (2房)
 $867万
 $20,300/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -76920,7 +76912,7 @@
           <t>G | 306呎 (1房)
 $594万
 $19,428/呎
-(26年-09月-05日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="I23" s="24" t="inlineStr">
@@ -76952,7 +76944,7 @@
           <t>L | 430呎 (2房)
 $930万
 $21,628/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="M23" s="24" t="inlineStr">
@@ -76960,7 +76952,7 @@
           <t>M | 481呎 (2房)
 $1058万
 $22,006/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="N23" s="24" t="inlineStr">
@@ -76968,7 +76960,7 @@
           <t>N | 288呎 (1房)
 $632万
 $21,951/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -77237,7 +77229,7 @@
           <t>E | 437呎 (2房)
 $969万
 $22,169/呎
-(26年-09月-04日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
@@ -77245,7 +77237,7 @@
           <t>F | 427呎 (2房)
 $854万
 $19,988/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -77261,7 +77253,7 @@
           <t>H | 305呎 (1房)
 $586万
 $19,200/呎
-(26年-09月-05日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="J26" s="24" t="inlineStr">
@@ -77293,7 +77285,7 @@
           <t>M | 481呎 (2房)
 $1042万
 $21,667/呎
-(26年-09月-05日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="N26" s="24" t="inlineStr">
@@ -77324,7 +77316,7 @@
           <t>B | 536呎 (2房)
 $1214万
 $22,646/呎
-(26年-09月-04日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
@@ -77372,7 +77364,7 @@
           <t>H | 305呎 (1房)
 $583万
 $19,102/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="J27" s="24" t="inlineStr">
@@ -77388,7 +77380,7 @@
           <t>K | 308呎 (1房)
 $602万
 $19,539/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="L27" s="24" t="inlineStr">
@@ -77546,7 +77538,7 @@
           <t>B | 536呎 (2房)
 $1191万
 $22,220/呎
-(26年-09月-07日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
@@ -77554,7 +77546,7 @@
           <t>C | 498呎 (2房)
 $1027万
 $20,618/呎
-(26年-09月-04日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
@@ -77681,7 +77673,7 @@
           <t>E | 437呎 (2房)
 $941万
 $21,529/呎
-(26年-09月-04日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
@@ -77689,7 +77681,7 @@
           <t>F | 427呎 (2房)
 $833万
 $19,501/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr">
@@ -77737,7 +77729,7 @@
           <t>M | 481呎 (2房)
 $1057万
 $21,979/呎
-(26年-09月-06日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="N30" s="24" t="inlineStr">
@@ -77745,7 +77737,7 @@
           <t>N | 288呎 (1房)
 $603万
 $20,938/呎
-(26年-09月-05日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -77919,7 +77911,7 @@
           <t>G | 306呎 (1房)
 $560万
 $18,301/呎
-(26年-09月-05日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="I32" s="24" t="inlineStr">
@@ -77951,7 +77943,7 @@
           <t>L | 430呎 (2房)
 $885万
 $20,572/呎
-(26年-09月-05日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="M32" s="24" t="inlineStr">
@@ -77959,7 +77951,7 @@
           <t>M | 481呎 (2房)
 $1006万
 $20,915/呎
-(26年-09月-07日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="N32" s="23" t="inlineStr">
@@ -78160,12 +78152,12 @@
 (26年-09月-19日)</t>
         </is>
       </c>
-      <c r="K34" s="23" t="inlineStr">
+      <c r="K34" s="24" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
-$771万
-$25,032/呎
-(在售)</t>
+$578万
+$18,776/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="L34" s="23" t="inlineStr">
@@ -81641,7 +81633,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -81651,7 +81643,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -83432,12 +83424,12 @@
 (26年-09月-15日)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>D | 432呎 (2房)
-招标单位
--
-(在售)</t>
+$989万
+$22,889/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
@@ -84111,7 +84103,7 @@
           <t>E | 499呎 (2房)
 $1083万
 $21,699/呎
-(26年-09月-05日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
@@ -84782,12 +84774,12 @@
 (26年-09月-17日)</t>
         </is>
       </c>
-      <c r="I32" s="23" t="inlineStr">
+      <c r="I32" s="24" t="inlineStr">
         <is>
           <t>H | 306呎 (1房)
-$773万
-$25,271/呎
-(在售)</t>
+$580万
+$18,954/呎
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="J32" s="24" t="inlineStr">
@@ -84806,12 +84798,12 @@
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="L32" s="23" t="inlineStr">
+      <c r="L32" s="24" t="inlineStr">
         <is>
           <t>L | 307呎 (1房)
-$757万
-$24,668/呎
-(在售)</t>
+$568万
+$18,502/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="M32" s="24" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -13050,23 +13050,23 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
-        <v>8128000</v>
+        <v>6096000</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>26562</v>
+        <v>19922</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K191" s="5" t="n">
@@ -13077,7 +13077,7 @@
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N191" s="3" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -13586,23 +13586,23 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
-        <v>14400000</v>
+        <v>10800000</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>29938</v>
+        <v>22453</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K199" s="5" t="n">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N199" s="3" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -16205,7 +16205,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -19169,7 +19169,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -19301,7 +19301,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -20242,34 +20242,34 @@
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
-        <v>13757000</v>
+        <v>10318000</v>
       </c>
       <c r="I303" s="5" t="n">
-        <v>28601</v>
+        <v>21451</v>
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K303" s="5" t="n">
-        <v>10317750</v>
+        <v>10318000</v>
       </c>
       <c r="L303" s="5" t="n">
         <v>21451</v>
       </c>
       <c r="M303" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N303" s="3" t="inlineStr">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="F305" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -20428,23 +20428,23 @@
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
-        <v>7784000</v>
+        <v>5838000</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>25521</v>
+        <v>19141</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K306" s="5" t="n">
@@ -20455,7 +20455,7 @@
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N306" s="3" t="inlineStr">
@@ -20490,34 +20490,34 @@
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
-        <v>7730000</v>
+        <v>5798000</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>25344</v>
+        <v>19010</v>
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K307" s="5" t="n">
-        <v>5797500</v>
+        <v>5798000</v>
       </c>
       <c r="L307" s="5" t="n">
-        <v>19008</v>
+        <v>19010</v>
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N307" s="3" t="inlineStr">
@@ -20552,34 +20552,34 @@
       </c>
       <c r="F308" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
-        <v>7730000</v>
+        <v>5798000</v>
       </c>
       <c r="I308" s="5" t="n">
-        <v>25261</v>
+        <v>18948</v>
       </c>
       <c r="J308" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K308" s="5" t="n">
-        <v>5797500</v>
+        <v>5798000</v>
       </c>
       <c r="L308" s="5" t="n">
-        <v>18946</v>
+        <v>18948</v>
       </c>
       <c r="M308" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N308" s="3" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="F309" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -21093,7 +21093,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -23171,7 +23171,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -23753,7 +23753,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -25256,34 +25256,34 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
-        <v>7874000</v>
+        <v>5906000</v>
       </c>
       <c r="I380" s="5" t="n">
-        <v>27340</v>
+        <v>20507</v>
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K380" s="5" t="n">
-        <v>5905500</v>
+        <v>5906000</v>
       </c>
       <c r="L380" s="5" t="n">
-        <v>20505</v>
+        <v>20507</v>
       </c>
       <c r="M380" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N380" s="3" t="inlineStr">
@@ -25690,34 +25690,34 @@
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
-        <v>10890000</v>
+        <v>8168000</v>
       </c>
       <c r="I387" s="5" t="n">
-        <v>25504</v>
+        <v>19129</v>
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K387" s="5" t="n">
-        <v>8167500</v>
+        <v>8168000</v>
       </c>
       <c r="L387" s="5" t="n">
-        <v>19128</v>
+        <v>19129</v>
       </c>
       <c r="M387" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N387" s="3" t="inlineStr">
@@ -74759,17 +74759,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -76024,7 +76024,7 @@
           <t>G | 306呎 (1房)
 $625万
 $20,418/呎
-(26年-09月-05日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="I15" s="24" t="inlineStr">
@@ -76270,7 +76270,7 @@
           <t>K | 308呎 (1房)
 $635万
 $20,623/呎
-(26年-09月-10日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="L17" s="23" t="inlineStr">
@@ -76357,7 +76357,7 @@
           <t>G | 306呎 (1房)
 $613万
 $20,020/呎
-(26年-09月-10日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="I18" s="24" t="inlineStr">
@@ -76373,7 +76373,7 @@
           <t>J | 305呎 (1房)
 $616万
 $20,207/呎
-(26年-09月-10日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="K18" s="24" t="inlineStr">
@@ -76381,7 +76381,7 @@
           <t>K | 308呎 (1房)
 $632万
 $20,519/呎
-(26年-09月-10日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="L18" s="23" t="inlineStr">
@@ -76397,7 +76397,7 @@
           <t>M | 481呎 (2房)
 $1091万
 $22,682/呎
-(26年-09月-10日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="N18" s="23" t="inlineStr">
@@ -76455,44 +76455,44 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
 $1184万
 $27,733/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
-$813万
-$26,562/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
+$610万
+$19,922/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
 $813万
 $26,649/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J19" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
 $818万
 $26,820/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K19" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="K19" s="23" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
 $838万
 $27,224/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -76503,12 +76503,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M19" s="22" t="inlineStr">
+      <c r="M19" s="23" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
 $1447万
 $30,083/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N19" s="22" t="inlineStr">
@@ -76595,7 +76595,7 @@
           <t>J | 305呎 (1房)
 $610万
 $20,016/呎
-(26年-09月-05日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="K20" s="24" t="inlineStr">
@@ -76614,12 +76614,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M20" s="23" t="inlineStr">
+      <c r="M20" s="24" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
-$1440万
-$29,938/呎
-(在售)</t>
+$1080万
+$22,453/呎
+(26年-09月-26日)</t>
         </is>
       </c>
       <c r="N20" s="23" t="inlineStr">
@@ -76936,7 +76936,7 @@
           <t>K | 308呎 (1房)
 $614万
 $19,919/呎
-(26年-09月-05日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="L23" s="24" t="inlineStr">
@@ -77197,7 +77197,7 @@
           <t>A | 771呎 (3房)
 $1793万
 $23,253/呎
-(26年-09月-04日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -77213,7 +77213,7 @@
           <t>C | 498呎 (2房)
 $1051万
 $21,100/呎
-(26年-09月-10日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -77269,7 +77269,7 @@
           <t>K | 308呎 (1房)
 $605万
 $19,630/呎
-(26年-09月-05日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="L26" s="24" t="inlineStr">
@@ -77388,7 +77388,7 @@
           <t>L | 430呎 (2房)
 $912万
 $21,205/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="M27" s="24" t="inlineStr">
@@ -77454,44 +77454,44 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
 $1127万
 $26,403/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
-$773万
-$25,261/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I28" s="22" t="inlineStr">
+$580万
+$18,948/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
-$773万
-$25,344/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J28" s="22" t="inlineStr">
+$580万
+$19,010/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="J28" s="24" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
-$778万
-$25,521/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K28" s="22" t="inlineStr">
+$584万
+$19,141/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
 $798万
 $25,912/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -77502,12 +77502,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M28" s="22" t="inlineStr">
+      <c r="M28" s="24" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
-$1376万
-$28,601/呎
-(已定价未售)</t>
+$1032万
+$21,451/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="N28" s="22" t="inlineStr">
@@ -77570,7 +77570,7 @@
           <t>F | 427呎 (2房)
 $837万
 $19,600/呎
-(26年-09月-05日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -77586,7 +77586,7 @@
           <t>H | 305呎 (1房)
 $574万
 $18,826/呎
-(26年-09月-05日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="J29" s="24" t="inlineStr">
@@ -77618,7 +77618,7 @@
           <t>M | 481呎 (2房)
 $1021万
 $21,233/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="N29" s="24" t="inlineStr">
@@ -77649,7 +77649,7 @@
           <t>B | 536呎 (2房)
 $1185万
 $22,108/呎
-(26年-09月-04日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -77713,7 +77713,7 @@
           <t>K | 308呎 (1房)
 $590万
 $19,140/呎
-(26年-09月-05日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="L30" s="23" t="inlineStr">
@@ -77784,7 +77784,7 @@
           <t>E | 437呎 (2房)
 $935万
 $21,391/呎
-(26年-09月-10日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
@@ -77927,7 +77927,7 @@
           <t>J | 305呎 (1房)
 $570万
 $18,672/呎
-(26年-09月-05日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="K32" s="24" t="inlineStr">
@@ -78120,12 +78120,12 @@
 (26年-09月-18日)</t>
         </is>
       </c>
-      <c r="G34" s="23" t="inlineStr">
+      <c r="G34" s="24" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
-$1089万
-$25,504/呎
-(在售)</t>
+$817万
+$19,129/呎
+(26年-09月-27日)</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -78176,12 +78176,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="N34" s="23" t="inlineStr">
+      <c r="N34" s="24" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
-$787万
-$27,340/呎
-(在售)</t>
+$591万
+$20,507/呎
+(26年-09月-28日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -1594,39 +1594,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H15" s="5" t="n">
+        <v>39064000</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>50667</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>29298000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>38000</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2464,39 +2456,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H28" s="5" t="n">
+        <v>33428000</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>43357</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>25071000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>32518</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3310,39 +3294,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H41" s="5" t="n">
+        <v>33097000</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>42927</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>24822750</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>32196</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4156,39 +4132,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H54" s="5" t="n">
+        <v>32769000</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>42502</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>24576750</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>31876</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5002,39 +4970,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H67" s="5" t="n">
+        <v>32445000</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>42082</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>24333750</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>31561</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6702,39 +6662,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H93" s="5" t="n">
+        <v>31806000</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>41253</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L93" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>23854500</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>30940</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7548,39 +7500,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H106" s="5" t="n">
+        <v>31242000</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>40521</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K106" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L106" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>23431500</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>30391</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7931,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -10463,7 +10407,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10587,7 +10531,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -11770,39 +11714,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I171" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H171" s="5" t="n">
+        <v>29726000</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>38555</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L171" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>22294500</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>28916</v>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N171" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12207,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12864,34 +12800,34 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
-        <v>8385000</v>
+        <v>6289000</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>27224</v>
+        <v>20419</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K188" s="5" t="n">
-        <v>6288750</v>
+        <v>6289000</v>
       </c>
       <c r="L188" s="5" t="n">
-        <v>20418</v>
+        <v>20419</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N188" s="3" t="inlineStr">
@@ -12926,23 +12862,23 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
-        <v>8180000</v>
+        <v>6135000</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>26820</v>
+        <v>20115</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K189" s="5" t="n">
@@ -12953,7 +12889,7 @@
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N189" s="3" t="inlineStr">
@@ -12988,23 +12924,23 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
-        <v>8128000</v>
+        <v>6096000</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>26649</v>
+        <v>19987</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K190" s="5" t="n">
@@ -13015,7 +12951,7 @@
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N190" s="3" t="inlineStr">
@@ -13112,34 +13048,34 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
-        <v>11842000</v>
+        <v>8882000</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>27733</v>
+        <v>20801</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K192" s="5" t="n">
-        <v>8881500</v>
+        <v>8882000</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>20800</v>
+        <v>20801</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N192" s="3" t="inlineStr">
@@ -14553,7 +14489,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14615,7 +14551,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -15499,7 +15435,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15623,7 +15559,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -16329,7 +16265,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -17889,7 +17825,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17951,7 +17887,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -18137,7 +18073,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -18479,7 +18415,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -18541,7 +18477,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -18789,7 +18725,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18913,7 +18849,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -19611,7 +19547,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -19735,7 +19671,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -19999,7 +19935,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -20123,7 +20059,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -20366,34 +20302,34 @@
       </c>
       <c r="F305" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
-        <v>7981000</v>
+        <v>5986000</v>
       </c>
       <c r="I305" s="5" t="n">
-        <v>25912</v>
+        <v>19435</v>
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K305" s="5" t="n">
-        <v>5985750</v>
+        <v>5986000</v>
       </c>
       <c r="L305" s="5" t="n">
-        <v>19434</v>
+        <v>19435</v>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N305" s="3" t="inlineStr">
@@ -20614,34 +20550,34 @@
       </c>
       <c r="F309" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
-        <v>11274000</v>
+        <v>8456000</v>
       </c>
       <c r="I309" s="5" t="n">
-        <v>26403</v>
+        <v>19803</v>
       </c>
       <c r="J309" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K309" s="5" t="n">
-        <v>8455500</v>
+        <v>8456000</v>
       </c>
       <c r="L309" s="5" t="n">
-        <v>19802</v>
+        <v>19803</v>
       </c>
       <c r="M309" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N309" s="3" t="inlineStr">
@@ -20964,39 +20900,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H314" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I314" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H314" s="5" t="n">
+        <v>26440000</v>
+      </c>
+      <c r="I314" s="5" t="n">
+        <v>34293</v>
       </c>
       <c r="J314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K314" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L314" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K314" s="5" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="L314" s="5" t="n">
+        <v>25720</v>
       </c>
       <c r="M314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21150,23 +21078,23 @@
       </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
-        <v>11956000</v>
+        <v>8967000</v>
       </c>
       <c r="I317" s="5" t="n">
-        <v>27805</v>
+        <v>20853</v>
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K317" s="5" t="n">
@@ -21177,7 +21105,7 @@
       </c>
       <c r="M317" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N317" s="3" t="inlineStr">
@@ -21217,7 +21145,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -21522,38 +21450,30 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H323" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I323" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H323" s="5" t="n">
+        <v>9456000</v>
+      </c>
+      <c r="I323" s="5" t="n">
+        <v>21638</v>
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K323" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L323" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K323" s="5" t="n">
+        <v>9456000</v>
+      </c>
+      <c r="L323" s="5" t="n">
+        <v>21638</v>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
@@ -21562,7 +21482,7 @@
       </c>
       <c r="N323" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21791,7 +21711,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -21972,23 +21892,23 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
-        <v>11900000</v>
+        <v>8925000</v>
       </c>
       <c r="I330" s="5" t="n">
-        <v>27674</v>
+        <v>20756</v>
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K330" s="5" t="n">
@@ -21999,7 +21919,7 @@
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N330" s="3" t="inlineStr">
@@ -22101,7 +22021,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -22163,7 +22083,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -22613,7 +22533,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -22737,7 +22657,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -22794,34 +22714,34 @@
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
-        <v>11834000</v>
+        <v>8876000</v>
       </c>
       <c r="I343" s="5" t="n">
-        <v>27521</v>
+        <v>20642</v>
       </c>
       <c r="J343" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K343" s="5" t="n">
-        <v>8875500</v>
+        <v>8876000</v>
       </c>
       <c r="L343" s="5" t="n">
-        <v>20641</v>
+        <v>20642</v>
       </c>
       <c r="M343" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N343" s="3" t="inlineStr">
@@ -22861,7 +22781,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22923,7 +22843,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22985,7 +22905,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -23109,7 +23029,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -23303,7 +23223,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -23500,23 +23420,23 @@
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
-        <v>7940000</v>
+        <v>5955000</v>
       </c>
       <c r="I354" s="5" t="n">
-        <v>27569</v>
+        <v>20677</v>
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K354" s="5" t="n">
@@ -23527,7 +23447,7 @@
       </c>
       <c r="M354" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N354" s="3" t="inlineStr">
@@ -24276,38 +24196,30 @@
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H366" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I366" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H366" s="5" t="n">
+        <v>17178000</v>
+      </c>
+      <c r="I366" s="5" t="n">
+        <v>22280</v>
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K366" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L366" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K366" s="5" t="n">
+        <v>17178000</v>
+      </c>
+      <c r="L366" s="5" t="n">
+        <v>22280</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
@@ -24316,7 +24228,7 @@
       </c>
       <c r="N366" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -25194,39 +25106,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H379" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I379" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H379" s="5" t="n">
+        <v>24917000</v>
+      </c>
+      <c r="I379" s="5" t="n">
+        <v>32318</v>
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K379" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L379" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K379" s="5" t="n">
+        <v>18687750</v>
+      </c>
+      <c r="L379" s="5" t="n">
+        <v>24238</v>
       </c>
       <c r="M379" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N379" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26656,12 +26560,12 @@
       </c>
       <c r="H401" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I401" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J401" s="3" t="inlineStr">
@@ -26671,12 +26575,12 @@
       </c>
       <c r="K401" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L401" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M401" s="3" t="inlineStr">
@@ -26686,7 +26590,7 @@
       </c>
       <c r="N401" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26934,39 +26838,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H405" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I405" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H405" s="5" t="n">
+        <v>36226000</v>
+      </c>
+      <c r="I405" s="5" t="n">
+        <v>50666</v>
       </c>
       <c r="J405" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K405" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L405" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K405" s="5" t="n">
+        <v>27169500</v>
+      </c>
+      <c r="L405" s="5" t="n">
+        <v>37999</v>
       </c>
       <c r="M405" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N405" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27566,12 +27462,12 @@
       </c>
       <c r="H414" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I414" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J414" s="3" t="inlineStr">
@@ -27581,12 +27477,12 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M414" s="3" t="inlineStr">
@@ -27596,7 +27492,7 @@
       </c>
       <c r="N414" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27844,39 +27740,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H418" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I418" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H418" s="5" t="n">
+        <v>30985000</v>
+      </c>
+      <c r="I418" s="5" t="n">
+        <v>43336</v>
       </c>
       <c r="J418" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K418" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L418" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K418" s="5" t="n">
+        <v>23238750</v>
+      </c>
+      <c r="L418" s="5" t="n">
+        <v>32502</v>
       </c>
       <c r="M418" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N418" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28476,12 +28364,12 @@
       </c>
       <c r="H427" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J427" s="3" t="inlineStr">
@@ -28491,12 +28379,12 @@
       </c>
       <c r="K427" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M427" s="3" t="inlineStr">
@@ -28506,7 +28394,7 @@
       </c>
       <c r="N427" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28754,39 +28642,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H431" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I431" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H431" s="5" t="n">
+        <v>30678000</v>
+      </c>
+      <c r="I431" s="5" t="n">
+        <v>42906</v>
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K431" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L431" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K431" s="5" t="n">
+        <v>23008500</v>
+      </c>
+      <c r="L431" s="5" t="n">
+        <v>32180</v>
       </c>
       <c r="M431" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N431" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -29386,12 +29266,12 @@
       </c>
       <c r="H440" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I440" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J440" s="3" t="inlineStr">
@@ -29401,12 +29281,12 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M440" s="3" t="inlineStr">
@@ -29416,7 +29296,7 @@
       </c>
       <c r="N440" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -29664,39 +29544,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H444" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I444" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H444" s="5" t="n">
+        <v>30374000</v>
+      </c>
+      <c r="I444" s="5" t="n">
+        <v>42481</v>
       </c>
       <c r="J444" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K444" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L444" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K444" s="5" t="n">
+        <v>22780500</v>
+      </c>
+      <c r="L444" s="5" t="n">
+        <v>31861</v>
       </c>
       <c r="M444" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N444" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -30296,12 +30168,12 @@
       </c>
       <c r="H453" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I453" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J453" s="3" t="inlineStr">
@@ -30311,12 +30183,12 @@
       </c>
       <c r="K453" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L453" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M453" s="3" t="inlineStr">
@@ -30326,7 +30198,7 @@
       </c>
       <c r="N453" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -30574,39 +30446,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H457" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I457" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H457" s="5" t="n">
+        <v>30073000</v>
+      </c>
+      <c r="I457" s="5" t="n">
+        <v>42060</v>
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K457" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L457" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K457" s="5" t="n">
+        <v>22554750</v>
+      </c>
+      <c r="L457" s="5" t="n">
+        <v>31545</v>
       </c>
       <c r="M457" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N457" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -31206,12 +31070,12 @@
       </c>
       <c r="H466" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I466" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J466" s="3" t="inlineStr">
@@ -31221,12 +31085,12 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M466" s="3" t="inlineStr">
@@ -31236,7 +31100,7 @@
       </c>
       <c r="N466" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -31484,39 +31348,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H470" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I470" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H470" s="5" t="n">
+        <v>29780000</v>
+      </c>
+      <c r="I470" s="5" t="n">
+        <v>41650</v>
       </c>
       <c r="J470" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K470" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L470" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K470" s="5" t="n">
+        <v>22335000</v>
+      </c>
+      <c r="L470" s="5" t="n">
+        <v>31238</v>
       </c>
       <c r="M470" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N470" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -32116,12 +31972,12 @@
       </c>
       <c r="H479" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I479" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J479" s="3" t="inlineStr">
@@ -32131,12 +31987,12 @@
       </c>
       <c r="K479" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L479" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M479" s="3" t="inlineStr">
@@ -32146,7 +32002,7 @@
       </c>
       <c r="N479" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -32394,39 +32250,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H483" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I483" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H483" s="5" t="n">
+        <v>29482000</v>
+      </c>
+      <c r="I483" s="5" t="n">
+        <v>41234</v>
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K483" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L483" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K483" s="5" t="n">
+        <v>22111500</v>
+      </c>
+      <c r="L483" s="5" t="n">
+        <v>30925</v>
       </c>
       <c r="M483" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N483" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -33026,12 +32874,12 @@
       </c>
       <c r="H492" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I492" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J492" s="3" t="inlineStr">
@@ -33041,12 +32889,12 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M492" s="3" t="inlineStr">
@@ -33056,7 +32904,7 @@
       </c>
       <c r="N492" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -33304,39 +33152,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H496" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I496" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H496" s="5" t="n">
+        <v>28960000</v>
+      </c>
+      <c r="I496" s="5" t="n">
+        <v>40503</v>
       </c>
       <c r="J496" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K496" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L496" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K496" s="5" t="n">
+        <v>21720000</v>
+      </c>
+      <c r="L496" s="5" t="n">
+        <v>30378</v>
       </c>
       <c r="M496" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N496" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -33936,12 +33776,12 @@
       </c>
       <c r="H505" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I505" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J505" s="3" t="inlineStr">
@@ -33951,12 +33791,12 @@
       </c>
       <c r="K505" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L505" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M505" s="3" t="inlineStr">
@@ -33966,7 +33806,7 @@
       </c>
       <c r="N505" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -34214,39 +34054,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H509" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I509" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H509" s="5" t="n">
+        <v>28673000</v>
+      </c>
+      <c r="I509" s="5" t="n">
+        <v>40102</v>
       </c>
       <c r="J509" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K509" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L509" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K509" s="5" t="n">
+        <v>21504750</v>
+      </c>
+      <c r="L509" s="5" t="n">
+        <v>30077</v>
       </c>
       <c r="M509" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N509" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -34846,12 +34678,12 @@
       </c>
       <c r="H518" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I518" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J518" s="3" t="inlineStr">
@@ -34861,12 +34693,12 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M518" s="3" t="inlineStr">
@@ -34876,7 +34708,7 @@
       </c>
       <c r="N518" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -35124,39 +34956,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H522" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I522" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H522" s="5" t="n">
+        <v>28389000</v>
+      </c>
+      <c r="I522" s="5" t="n">
+        <v>39705</v>
       </c>
       <c r="J522" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K522" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L522" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K522" s="5" t="n">
+        <v>21291750</v>
+      </c>
+      <c r="L522" s="5" t="n">
+        <v>29779</v>
       </c>
       <c r="M522" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N522" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -35756,12 +35580,12 @@
       </c>
       <c r="H531" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I531" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J531" s="3" t="inlineStr">
@@ -35771,12 +35595,12 @@
       </c>
       <c r="K531" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L531" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M531" s="3" t="inlineStr">
@@ -35786,7 +35610,7 @@
       </c>
       <c r="N531" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -36034,39 +35858,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H535" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I535" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H535" s="5" t="n">
+        <v>28109000</v>
+      </c>
+      <c r="I535" s="5" t="n">
+        <v>39313</v>
       </c>
       <c r="J535" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K535" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L535" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K535" s="5" t="n">
+        <v>21081750</v>
+      </c>
+      <c r="L535" s="5" t="n">
+        <v>29485</v>
       </c>
       <c r="M535" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N535" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -36666,12 +36482,12 @@
       </c>
       <c r="H544" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I544" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J544" s="3" t="inlineStr">
@@ -36681,12 +36497,12 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M544" s="3" t="inlineStr">
@@ -36696,7 +36512,7 @@
       </c>
       <c r="N544" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -36944,39 +36760,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H548" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I548" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H548" s="5" t="n">
+        <v>27829000</v>
+      </c>
+      <c r="I548" s="5" t="n">
+        <v>38922</v>
       </c>
       <c r="J548" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K548" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L548" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K548" s="5" t="n">
+        <v>20871750</v>
+      </c>
+      <c r="L548" s="5" t="n">
+        <v>29191</v>
       </c>
       <c r="M548" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N548" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -37576,12 +37384,12 @@
       </c>
       <c r="H557" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I557" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J557" s="3" t="inlineStr">
@@ -37591,12 +37399,12 @@
       </c>
       <c r="K557" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L557" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M557" s="3" t="inlineStr">
@@ -37606,7 +37414,7 @@
       </c>
       <c r="N557" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -37854,39 +37662,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H561" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I561" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H561" s="5" t="n">
+        <v>27553000</v>
+      </c>
+      <c r="I561" s="5" t="n">
+        <v>38536</v>
       </c>
       <c r="J561" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K561" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L561" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K561" s="5" t="n">
+        <v>20664750</v>
+      </c>
+      <c r="L561" s="5" t="n">
+        <v>28902</v>
       </c>
       <c r="M561" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N561" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38486,12 +38286,12 @@
       </c>
       <c r="H570" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I570" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J570" s="3" t="inlineStr">
@@ -38501,12 +38301,12 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M570" s="3" t="inlineStr">
@@ -38516,7 +38316,7 @@
       </c>
       <c r="N570" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38764,39 +38564,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H574" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I574" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H574" s="5" t="n">
+        <v>27280000</v>
+      </c>
+      <c r="I574" s="5" t="n">
+        <v>38154</v>
       </c>
       <c r="J574" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K574" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L574" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K574" s="5" t="n">
+        <v>20460000</v>
+      </c>
+      <c r="L574" s="5" t="n">
+        <v>28615</v>
       </c>
       <c r="M574" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N574" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39396,12 +39188,12 @@
       </c>
       <c r="H583" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I583" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J583" s="3" t="inlineStr">
@@ -39411,12 +39203,12 @@
       </c>
       <c r="K583" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L583" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M583" s="3" t="inlineStr">
@@ -39426,7 +39218,7 @@
       </c>
       <c r="N583" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39674,39 +39466,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H587" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I587" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H587" s="5" t="n">
+        <v>27008000</v>
+      </c>
+      <c r="I587" s="5" t="n">
+        <v>37773</v>
       </c>
       <c r="J587" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K587" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L587" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K587" s="5" t="n">
+        <v>20256000</v>
+      </c>
+      <c r="L587" s="5" t="n">
+        <v>28330</v>
       </c>
       <c r="M587" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N587" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -40306,12 +40090,12 @@
       </c>
       <c r="H596" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I596" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J596" s="3" t="inlineStr">
@@ -40321,12 +40105,12 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M596" s="3" t="inlineStr">
@@ -40336,7 +40120,7 @@
       </c>
       <c r="N596" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -40584,39 +40368,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H600" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I600" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H600" s="5" t="n">
+        <v>26741000</v>
+      </c>
+      <c r="I600" s="5" t="n">
+        <v>37400</v>
       </c>
       <c r="J600" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K600" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L600" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K600" s="5" t="n">
+        <v>20055750</v>
+      </c>
+      <c r="L600" s="5" t="n">
+        <v>28050</v>
       </c>
       <c r="M600" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N600" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -41216,12 +40992,12 @@
       </c>
       <c r="H609" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I609" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J609" s="3" t="inlineStr">
@@ -41231,12 +41007,12 @@
       </c>
       <c r="K609" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L609" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M609" s="3" t="inlineStr">
@@ -41246,7 +41022,7 @@
       </c>
       <c r="N609" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -41494,39 +41270,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H613" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I613" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H613" s="5" t="n">
+        <v>26278000</v>
+      </c>
+      <c r="I613" s="5" t="n">
+        <v>36752</v>
       </c>
       <c r="J613" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K613" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L613" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K613" s="5" t="n">
+        <v>19708500</v>
+      </c>
+      <c r="L613" s="5" t="n">
+        <v>27564</v>
       </c>
       <c r="M613" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N613" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -42126,12 +41894,12 @@
       </c>
       <c r="H622" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I622" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J622" s="3" t="inlineStr">
@@ -42141,12 +41909,12 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M622" s="3" t="inlineStr">
@@ -42156,7 +41924,7 @@
       </c>
       <c r="N622" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -42404,39 +42172,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H626" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I626" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H626" s="5" t="n">
+        <v>26016000</v>
+      </c>
+      <c r="I626" s="5" t="n">
+        <v>36386</v>
       </c>
       <c r="J626" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K626" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L626" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K626" s="5" t="n">
+        <v>19512000</v>
+      </c>
+      <c r="L626" s="5" t="n">
+        <v>27290</v>
       </c>
       <c r="M626" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N626" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -43036,12 +42796,12 @@
       </c>
       <c r="H635" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I635" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J635" s="3" t="inlineStr">
@@ -43051,12 +42811,12 @@
       </c>
       <c r="K635" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L635" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M635" s="3" t="inlineStr">
@@ -43066,7 +42826,7 @@
       </c>
       <c r="N635" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -43314,39 +43074,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H639" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I639" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H639" s="5" t="n">
+        <v>25758000</v>
+      </c>
+      <c r="I639" s="5" t="n">
+        <v>36025</v>
       </c>
       <c r="J639" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K639" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L639" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K639" s="5" t="n">
+        <v>19318500</v>
+      </c>
+      <c r="L639" s="5" t="n">
+        <v>27019</v>
       </c>
       <c r="M639" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N639" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -43946,12 +43698,12 @@
       </c>
       <c r="H648" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I648" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J648" s="3" t="inlineStr">
@@ -43961,12 +43713,12 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M648" s="3" t="inlineStr">
@@ -43976,7 +43728,7 @@
       </c>
       <c r="N648" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -44224,39 +43976,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H652" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I652" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H652" s="5" t="n">
+        <v>25501000</v>
+      </c>
+      <c r="I652" s="5" t="n">
+        <v>35666</v>
       </c>
       <c r="J652" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K652" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L652" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K652" s="5" t="n">
+        <v>19125750</v>
+      </c>
+      <c r="L652" s="5" t="n">
+        <v>26749</v>
       </c>
       <c r="M652" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N652" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -44856,12 +44600,12 @@
       </c>
       <c r="H661" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I661" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J661" s="3" t="inlineStr">
@@ -44871,12 +44615,12 @@
       </c>
       <c r="K661" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L661" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M661" s="3" t="inlineStr">
@@ -44886,7 +44630,7 @@
       </c>
       <c r="N661" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -45134,39 +44878,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H665" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I665" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H665" s="5" t="n">
+        <v>25252000</v>
+      </c>
+      <c r="I665" s="5" t="n">
+        <v>35317</v>
       </c>
       <c r="J665" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K665" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L665" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K665" s="5" t="n">
+        <v>18939000</v>
+      </c>
+      <c r="L665" s="5" t="n">
+        <v>26488</v>
       </c>
       <c r="M665" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N665" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -45766,12 +45502,12 @@
       </c>
       <c r="H674" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I674" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J674" s="3" t="inlineStr">
@@ -45781,12 +45517,12 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M674" s="3" t="inlineStr">
@@ -45796,7 +45532,7 @@
       </c>
       <c r="N674" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -46044,39 +45780,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H678" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I678" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H678" s="5" t="n">
+        <v>25002000</v>
+      </c>
+      <c r="I678" s="5" t="n">
+        <v>34968</v>
       </c>
       <c r="J678" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K678" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L678" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K678" s="5" t="n">
+        <v>18751500</v>
+      </c>
+      <c r="L678" s="5" t="n">
+        <v>26226</v>
       </c>
       <c r="M678" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N678" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -46676,12 +46404,12 @@
       </c>
       <c r="H687" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I687" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J687" s="3" t="inlineStr">
@@ -46691,12 +46419,12 @@
       </c>
       <c r="K687" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L687" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M687" s="3" t="inlineStr">
@@ -46706,7 +46434,7 @@
       </c>
       <c r="N687" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -46954,39 +46682,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H691" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I691" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H691" s="5" t="n">
+        <v>24888000</v>
+      </c>
+      <c r="I691" s="5" t="n">
+        <v>34615</v>
       </c>
       <c r="J691" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K691" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L691" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K691" s="5" t="n">
+        <v>18666000</v>
+      </c>
+      <c r="L691" s="5" t="n">
+        <v>25961</v>
       </c>
       <c r="M691" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N691" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -47586,12 +47306,12 @@
       </c>
       <c r="H700" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I700" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J700" s="3" t="inlineStr">
@@ -47601,12 +47321,12 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M700" s="3" t="inlineStr">
@@ -47616,7 +47336,7 @@
       </c>
       <c r="N700" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -47864,39 +47584,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H704" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I704" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H704" s="5" t="n">
+        <v>24642000</v>
+      </c>
+      <c r="I704" s="5" t="n">
+        <v>34273</v>
       </c>
       <c r="J704" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K704" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L704" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K704" s="5" t="n">
+        <v>18481500</v>
+      </c>
+      <c r="L704" s="5" t="n">
+        <v>25704</v>
       </c>
       <c r="M704" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N704" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -48426,12 +48138,12 @@
       </c>
       <c r="H712" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I712" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J712" s="3" t="inlineStr">
@@ -48441,12 +48153,12 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M712" s="3" t="inlineStr">
@@ -48456,7 +48168,7 @@
       </c>
       <c r="N712" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -48704,39 +48416,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H716" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I716" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H716" s="5" t="n">
+        <v>24669000</v>
+      </c>
+      <c r="I716" s="5" t="n">
+        <v>33609</v>
       </c>
       <c r="J716" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K716" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L716" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K716" s="5" t="n">
+        <v>18501750</v>
+      </c>
+      <c r="L716" s="5" t="n">
+        <v>25207</v>
       </c>
       <c r="M716" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N716" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -49126,12 +48830,12 @@
       </c>
       <c r="H722" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I722" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J722" s="3" t="inlineStr">
@@ -49141,12 +48845,12 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M722" s="3" t="inlineStr">
@@ -49156,7 +48860,7 @@
       </c>
       <c r="N722" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -49404,39 +49108,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H726" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I726" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H726" s="5" t="n">
+        <v>24424000</v>
+      </c>
+      <c r="I726" s="5" t="n">
+        <v>33275</v>
       </c>
       <c r="J726" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K726" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L726" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K726" s="5" t="n">
+        <v>18318000</v>
+      </c>
+      <c r="L726" s="5" t="n">
+        <v>24956</v>
       </c>
       <c r="M726" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N726" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -49826,12 +49522,12 @@
       </c>
       <c r="H732" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I732" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J732" s="3" t="inlineStr">
@@ -49841,12 +49537,12 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L732" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M732" s="3" t="inlineStr">
@@ -49856,7 +49552,7 @@
       </c>
       <c r="N732" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -50104,39 +49800,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H736" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I736" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H736" s="5" t="n">
+        <v>24180000</v>
+      </c>
+      <c r="I736" s="5" t="n">
+        <v>32943</v>
       </c>
       <c r="J736" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K736" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L736" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K736" s="5" t="n">
+        <v>18135000</v>
+      </c>
+      <c r="L736" s="5" t="n">
+        <v>24707</v>
       </c>
       <c r="M736" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N736" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -50526,12 +50214,12 @@
       </c>
       <c r="H742" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I742" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J742" s="3" t="inlineStr">
@@ -50541,12 +50229,12 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L742" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M742" s="3" t="inlineStr">
@@ -50556,7 +50244,7 @@
       </c>
       <c r="N742" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -50804,39 +50492,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H746" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I746" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H746" s="5" t="n">
+        <v>23264000</v>
+      </c>
+      <c r="I746" s="5" t="n">
+        <v>32628</v>
       </c>
       <c r="J746" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K746" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L746" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K746" s="5" t="n">
+        <v>17448000</v>
+      </c>
+      <c r="L746" s="5" t="n">
+        <v>24471</v>
       </c>
       <c r="M746" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N746" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -51086,12 +50766,12 @@
       </c>
       <c r="H750" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I750" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J750" s="3" t="inlineStr">
@@ -51101,12 +50781,12 @@
       </c>
       <c r="K750" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L750" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M750" s="3" t="inlineStr">
@@ -51116,7 +50796,7 @@
       </c>
       <c r="N750" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -51364,39 +51044,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H754" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I754" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H754" s="5" t="n">
+        <v>23026000</v>
+      </c>
+      <c r="I754" s="5" t="n">
+        <v>32295</v>
       </c>
       <c r="J754" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K754" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L754" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K754" s="5" t="n">
+        <v>17269500</v>
+      </c>
+      <c r="L754" s="5" t="n">
+        <v>24221</v>
       </c>
       <c r="M754" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N754" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -51646,12 +51318,12 @@
       </c>
       <c r="H758" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I758" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J758" s="3" t="inlineStr">
@@ -51661,12 +51333,12 @@
       </c>
       <c r="K758" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L758" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M758" s="3" t="inlineStr">
@@ -51676,7 +51348,7 @@
       </c>
       <c r="N758" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -51924,39 +51596,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H762" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I762" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H762" s="5" t="n">
+        <v>23170000</v>
+      </c>
+      <c r="I762" s="5" t="n">
+        <v>32003</v>
       </c>
       <c r="J762" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K762" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L762" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K762" s="5" t="n">
+        <v>17377500</v>
+      </c>
+      <c r="L762" s="5" t="n">
+        <v>24002</v>
       </c>
       <c r="M762" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>置輕鬆置簡單120天付款計劃</t>
         </is>
       </c>
       <c r="N762" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -74759,7 +74423,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -74769,7 +74433,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>163</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -74864,8 +74528,8 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
+$3906万
+$50,667/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -74975,8 +74639,8 @@
       <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
+$3343万
+$43,357/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -75086,8 +74750,8 @@
       <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
+$3310万
+$42,927/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -75197,8 +74861,8 @@
       <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
+$3277万
+$42,502/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -75308,8 +74972,8 @@
       <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
+$3244万
+$42,082/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -75530,8 +75194,8 @@
       <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
+$3181万
+$41,253/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -75641,8 +75305,8 @@
       <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
+$3124万
+$40,521/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -75802,7 +75466,7 @@
           <t>G | 306呎 (1房)
 $637万
 $20,827/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="I13" s="24" t="inlineStr">
@@ -76127,7 +75791,7 @@
           <t>F | 427呎 (2房)
 $902万
 $21,119/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -76143,7 +75807,7 @@
           <t>H | 305呎 (1房)
 $619万
 $20,282/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="J16" s="24" t="inlineStr">
@@ -76196,8 +75860,8 @@
       <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
+$2973万
+$38,555/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -76349,7 +76013,7 @@
           <t>F | 427呎 (2房)
 $893万
 $20,909/呎
-(26年-09月-13日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -76455,12 +76119,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="G19" s="24" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
-$1184万
-$27,733/呎
-(在售)</t>
+$888万
+$20,801/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -76471,28 +76135,28 @@
 (26年-09月-28日)</t>
         </is>
       </c>
-      <c r="I19" s="23" t="inlineStr">
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
-$813万
-$26,649/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J19" s="23" t="inlineStr">
+$610万
+$19,987/呎
+(26年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="J19" s="24" t="inlineStr">
         <is>
           <t>J | 305呎 (1房)
-$818万
-$26,820/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K19" s="23" t="inlineStr">
+$614万
+$20,115/呎
+(26年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="K19" s="24" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
-$838万
-$27,224/呎
-(在售)</t>
+$629万
+$20,419/呎
+(26年-10月-03日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -76706,7 +76370,7 @@
           <t>J | 305呎 (1房)
 $604万
 $19,820/呎
-(26年-09月-06日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="K21" s="24" t="inlineStr">
@@ -76714,7 +76378,7 @@
           <t>K | 308呎 (1房)
 $620万
 $20,117/呎
-(26年-09月-08日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="L21" s="24" t="inlineStr">
@@ -76793,7 +76457,7 @@
           <t>F | 427呎 (2房)
 $871万
 $20,393/呎
-(26年-09月-05日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -76809,7 +76473,7 @@
           <t>H | 305呎 (1房)
 $598万
 $19,593/呎
-(26年-09月-05日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="J22" s="24" t="inlineStr">
@@ -76920,7 +76584,7 @@
           <t>H | 305呎 (1房)
 $618万
 $20,272/呎
-(26年-09月-05日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="J23" s="24" t="inlineStr">
@@ -77086,7 +76750,7 @@
           <t>A | 771呎 (3房)
 $1807万
 $23,435/呎
-(26年-09月-11日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -77126,7 +76790,7 @@
           <t>F | 427呎 (2房)
 $858万
 $20,089/呎
-(26年-09月-13日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -77150,7 +76814,7 @@
           <t>J | 305呎 (1房)
 $593万
 $19,433/呎
-(26年-09月-10日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="K25" s="24" t="inlineStr">
@@ -77158,7 +76822,7 @@
           <t>K | 308呎 (1房)
 $607万
 $19,718/呎
-(26年-09月-10日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="L25" s="23" t="inlineStr">
@@ -77245,7 +76909,7 @@
           <t>G | 306呎 (1房)
 $586万
 $19,137/呎
-(26年-09月-05日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="I26" s="24" t="inlineStr">
@@ -77261,7 +76925,7 @@
           <t>J | 305呎 (1房)
 $590万
 $19,328/呎
-(26年-09月-05日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="K26" s="24" t="inlineStr">
@@ -77293,7 +76957,7 @@
           <t>N | 288呎 (1房)
 $622万
 $21,583/呎
-(26年-09月-05日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -77308,7 +76972,7 @@
           <t>A | 771呎 (3房)
 $1783万
 $23,123/呎
-(26年-09月-04日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -77324,7 +76988,7 @@
           <t>C | 498呎 (2房)
 $1045万
 $20,980/呎
-(26年-09月-04日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -77356,7 +77020,7 @@
           <t>G | 306呎 (1房)
 $583万
 $19,039/呎
-(26年-09月-05日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="I27" s="24" t="inlineStr">
@@ -77372,7 +77036,7 @@
           <t>J | 305呎 (1房)
 $587万
 $19,233/呎
-(26年-09月-05日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="K27" s="24" t="inlineStr">
@@ -77417,8 +77081,8 @@
       <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
+$2644万
+$34,293/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -77454,12 +77118,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="G28" s="24" t="inlineStr">
         <is>
           <t>F | 427呎 (2房)
-$1127万
-$26,403/呎
-(在售)</t>
+$846万
+$19,803/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
@@ -77486,12 +77150,12 @@
 (26年-09月-28日)</t>
         </is>
       </c>
-      <c r="K28" s="23" t="inlineStr">
+      <c r="K28" s="24" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
-$798万
-$25,912/呎
-(在售)</t>
+$599万
+$19,435/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -77530,7 +77194,7 @@
           <t>A | 771呎 (3房)
 $1750万
 $22,695/呎
-(26年-09月-16日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -77557,12 +77221,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F29" s="24" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
-招标单位
--
-(在售)</t>
+$946万
+$21,638/呎
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
@@ -77602,15 +77266,15 @@
           <t>K | 308呎 (1房)
 $592万
 $19,237/呎
-(26年-09月-05日)</t>
-        </is>
-      </c>
-      <c r="L29" s="23" t="inlineStr">
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="L29" s="24" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
-$1196万
-$27,805/呎
-(在售)</t>
+$897万
+$20,853/呎
+(26年-10月-03日)</t>
         </is>
       </c>
       <c r="M29" s="24" t="inlineStr">
@@ -77641,7 +77305,7 @@
           <t>A | 771呎 (3房)
 $1739万
 $22,553/呎
-(26年-09月-13日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -77697,7 +77361,7 @@
           <t>H | 305呎 (1房)
 $572万
 $18,738/呎
-(26年-09月-05日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="J30" s="24" t="inlineStr">
@@ -77705,7 +77369,7 @@
           <t>J | 305呎 (1房)
 $575万
 $18,852/呎
-(26年-09月-13日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="K30" s="24" t="inlineStr">
@@ -77716,12 +77380,12 @@
 (26年-09月-28日)</t>
         </is>
       </c>
-      <c r="L30" s="23" t="inlineStr">
+      <c r="L30" s="24" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
-$1190万
-$27,674/呎
-(在售)</t>
+$892万
+$20,756/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="M30" s="24" t="inlineStr">
@@ -77768,7 +77432,7 @@
           <t>C | 498呎 (2房)
 $1014万
 $20,357/呎
-(26年-09月-11日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -77792,7 +77456,7 @@
           <t>F | 427呎 (2房)
 $829万
 $19,410/呎
-(26年-09月-17日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
@@ -77808,7 +77472,7 @@
           <t>H | 305呎 (1房)
 $569万
 $18,649/呎
-(26年-09月-10日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="J31" s="24" t="inlineStr">
@@ -77816,7 +77480,7 @@
           <t>J | 305呎 (1房)
 $572万
 $18,761/呎
-(26年-09月-10日)</t>
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="K31" s="24" t="inlineStr">
@@ -77824,15 +77488,15 @@
           <t>K | 308呎 (1房)
 $587万
 $19,045/呎
-(26年-09月-10日)</t>
-        </is>
-      </c>
-      <c r="L31" s="23" t="inlineStr">
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="L31" s="24" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
-$1183万
-$27,521/呎
-(在售)</t>
+$888万
+$20,642/呎
+(26年-10月-03日)</t>
         </is>
       </c>
       <c r="M31" s="24" t="inlineStr">
@@ -77840,7 +77504,7 @@
           <t>M | 481呎 (2房)
 $1011万
 $21,023/呎
-(26年-09月-16日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
@@ -77858,12 +77522,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
-(在售)</t>
+$1718万
+$22,280/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -77954,12 +77618,12 @@
 (26年-09月-23日)</t>
         </is>
       </c>
-      <c r="N32" s="23" t="inlineStr">
+      <c r="N32" s="24" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
-$794万
-$27,569/呎
-(在售)</t>
+$596万
+$20,677/呎
+(26年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -77972,8 +77636,8 @@
       <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
+$2492万
+$32,318/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -78371,8 +78035,8 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$3623万
+$50,666/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -78403,7 +78067,7 @@
       <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -78482,8 +78146,8 @@
       <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$3098万
+$43,336/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -78514,7 +78178,7 @@
       <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -78593,8 +78257,8 @@
       <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$3068万
+$42,906/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -78625,7 +78289,7 @@
       <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -78704,8 +78368,8 @@
       <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$3037万
+$42,481/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -78736,7 +78400,7 @@
       <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -78815,8 +78479,8 @@
       <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$3007万
+$42,060/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -78847,7 +78511,7 @@
       <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -78926,8 +78590,8 @@
       <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2978万
+$41,650/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -78958,7 +78622,7 @@
       <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -79037,8 +78701,8 @@
       <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2948万
+$41,234/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -79069,7 +78733,7 @@
       <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -79148,8 +78812,8 @@
       <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2896万
+$40,503/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -79180,7 +78844,7 @@
       <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -79259,8 +78923,8 @@
       <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2867万
+$40,102/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -79291,7 +78955,7 @@
       <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -79370,8 +79034,8 @@
       <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2839万
+$39,705/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -79402,7 +79066,7 @@
       <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -79481,8 +79145,8 @@
       <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2811万
+$39,313/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -79513,7 +79177,7 @@
       <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -79592,8 +79256,8 @@
       <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2783万
+$38,922/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -79624,7 +79288,7 @@
       <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -79703,8 +79367,8 @@
       <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2755万
+$38,536/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -79735,7 +79399,7 @@
       <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -79814,8 +79478,8 @@
       <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2728万
+$38,154/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -79846,7 +79510,7 @@
       <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -79925,8 +79589,8 @@
       <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2701万
+$37,773/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -79957,7 +79621,7 @@
       <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -80036,8 +79700,8 @@
       <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2674万
+$37,400/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -80068,7 +79732,7 @@
       <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -80147,8 +79811,8 @@
       <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2628万
+$36,752/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -80179,7 +79843,7 @@
       <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -80258,8 +79922,8 @@
       <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2602万
+$36,386/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -80290,7 +79954,7 @@
       <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -80369,8 +80033,8 @@
       <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2576万
+$36,025/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -80401,7 +80065,7 @@
       <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -80480,8 +80144,8 @@
       <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2550万
+$35,666/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -80512,7 +80176,7 @@
       <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -80591,8 +80255,8 @@
       <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2525万
+$35,317/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -80623,7 +80287,7 @@
       <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -80702,8 +80366,8 @@
       <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 715呎 (3房)
-招标单位
--
+$2500万
+$34,968/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -80734,7 +80398,7 @@
       <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -80813,8 +80477,8 @@
       <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 719呎 (3房)
-招标单位
--
+$2489万
+$34,615/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -80845,7 +80509,7 @@
       <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -80924,8 +80588,8 @@
       <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 719呎 (3房)
-招标单位
--
+$2464万
+$34,273/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -80956,7 +80620,7 @@
       <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -81035,8 +80699,8 @@
       <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 734呎 (3房)
-招标单位
--
+$2467万
+$33,609/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -81067,7 +80731,7 @@
       <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -81139,8 +80803,8 @@
       <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 734呎 (3房)
-招标单位
--
+$2442万
+$33,275/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -81171,7 +80835,7 @@
       <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -81229,8 +80893,8 @@
       <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 734呎 (3房)
-招标单位
--
+$2418万
+$32,943/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -81261,7 +80925,7 @@
       <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -81319,8 +80983,8 @@
       <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-招标单位
--
+$2326万
+$32,628/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -81351,7 +81015,7 @@
       <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -81409,8 +81073,8 @@
       <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-招标单位
--
+$2303万
+$32,295/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -81441,7 +81105,7 @@
       <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -81485,8 +81149,8 @@
       <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 724呎 (3房)
-招标单位
--
+$2317万
+$32,003/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -81517,7 +81181,7 @@
       <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -7745,7 +7745,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -17564,38 +17564,30 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H262" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I262" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H262" s="5" t="n">
+        <v>18188000</v>
+      </c>
+      <c r="I262" s="5" t="n">
+        <v>23590</v>
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K262" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L262" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K262" s="5" t="n">
+        <v>18188000</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>23590</v>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
@@ -17604,7 +17596,7 @@
       </c>
       <c r="N262" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17639,7 +17631,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17701,7 +17693,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17949,7 +17941,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -22590,34 +22582,34 @@
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
-        <v>7994000</v>
+        <v>5996000</v>
       </c>
       <c r="I341" s="5" t="n">
-        <v>27757</v>
+        <v>20819</v>
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K341" s="5" t="n">
-        <v>5995500</v>
+        <v>5996000</v>
       </c>
       <c r="L341" s="5" t="n">
-        <v>20818</v>
+        <v>20819</v>
       </c>
       <c r="M341" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N341" s="3" t="inlineStr">
@@ -23350,38 +23342,30 @@
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H353" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I353" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H353" s="5" t="n">
+        <v>17288000</v>
+      </c>
+      <c r="I353" s="5" t="n">
+        <v>22423</v>
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K353" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L353" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K353" s="5" t="n">
+        <v>17288000</v>
+      </c>
+      <c r="L353" s="5" t="n">
+        <v>22423</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
@@ -23390,7 +23374,7 @@
       </c>
       <c r="N353" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -25475,7 +25459,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -25661,7 +25645,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -64739,7 +64723,7 @@
       </c>
       <c r="G969" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H969" s="5" t="n">
@@ -69454,38 +69438,30 @@
       </c>
       <c r="F1045" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1045" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1045" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1045" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H1045" s="5" t="n">
+        <v>9688000</v>
+      </c>
+      <c r="I1045" s="5" t="n">
+        <v>22426</v>
       </c>
       <c r="J1045" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K1045" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L1045" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K1045" s="5" t="n">
+        <v>9688000</v>
+      </c>
+      <c r="L1045" s="5" t="n">
+        <v>22426</v>
       </c>
       <c r="M1045" s="3" t="inlineStr">
         <is>
@@ -69494,7 +69470,7 @@
       </c>
       <c r="N1045" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -73939,7 +73915,7 @@
       </c>
       <c r="G1117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H1117" s="5" t="n">
@@ -74063,7 +74039,7 @@
       </c>
       <c r="G1119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H1119" s="5" t="n">
@@ -74125,7 +74101,7 @@
       </c>
       <c r="G1120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H1120" s="5" t="n">
@@ -74423,7 +74399,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -74433,7 +74409,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>166</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -75458,7 +75434,7 @@
           <t>F | 427呎 (2房)
 $929万
 $21,761/呎
-(26年-09月-10日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -75490,7 +75466,7 @@
           <t>K | 308呎 (1房)
 $658万
 $21,347/呎
-(26年-09月-18日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="L13" s="23" t="inlineStr">
@@ -75720,7 +75696,7 @@
           <t>L | 430呎 (2房)
 $978万
 $22,756/呎
-(26年-09月-05日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="M15" s="23" t="inlineStr">
@@ -75799,7 +75775,7 @@
           <t>G | 306呎 (1房)
 $619万
 $20,216/呎
-(26年-09月-05日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="I16" s="24" t="inlineStr">
@@ -75926,7 +75902,7 @@
           <t>J | 305呎 (1房)
 $620万
 $20,311/呎
-(26年-09月-09日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="K17" s="24" t="inlineStr">
@@ -76306,7 +76282,7 @@
           <t>A | 771呎 (3房)
 $1855万
 $24,060/呎
-(26年-09月-04日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
@@ -76417,7 +76393,7 @@
           <t>A | 771呎 (3房)
 $1843万
 $23,901/呎
-(26年-09月-04日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -76634,12 +76610,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
-(在售)</t>
+$1819万
+$23,590/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -76806,7 +76782,7 @@
           <t>H | 305呎 (1房)
 $589万
 $19,298/呎
-(26年-09月-10日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="J25" s="24" t="inlineStr">
@@ -76838,7 +76814,7 @@
           <t>M | 481呎 (2房)
 $1048万
 $21,778/呎
-(26年-09月-18日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="N25" s="24" t="inlineStr">
@@ -76846,7 +76822,7 @@
           <t>N | 288呎 (1房)
 $625万
 $21,688/呎
-(26年-09月-18日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -77411,12 +77387,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
-(在售)</t>
+$1729万
+$22,423/呎
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -77507,12 +77483,12 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="N31" s="23" t="inlineStr">
+      <c r="N31" s="24" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
-$799万
-$27,757/呎
-(在售)</t>
+$600万
+$20,819/呎
+(26年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -77781,7 +77757,7 @@
           <t>E | 437呎 (2房)
 $918万
 $21,002/呎
-(26年-09月-18日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
@@ -77805,7 +77781,7 @@
           <t>H | 305呎 (1房)
 $560万
 $18,361/呎
-(26年-09月-15日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="J34" s="24" t="inlineStr">
@@ -81297,7 +81273,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -81307,7 +81283,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -83077,7 +83053,7 @@
           <t>B | 486呎 (2房)
 $1149万
 $23,638/呎
-(26年-09月-05日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
@@ -83754,12 +83730,12 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>D | 432呎 (2房)
-招标单位
--
-(在售)</t>
+$969万
+$22,426/呎
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
@@ -84427,7 +84403,7 @@
           <t>F | 307呎 (1房)
 $572万
 $18,632/呎
-(26年-09月-17日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -84435,7 +84411,7 @@
           <t>G | 306呎 (1房)
 $572万
 $18,693/呎
-(26年-09月-17日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="I32" s="24" t="inlineStr">
@@ -84451,7 +84427,7 @@
           <t>J | 308呎 (1房)
 $580万
 $18,831/呎
-(26年-09月-21日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="K32" s="24" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -5396,23 +5396,23 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>8756000</v>
+        <v>6567000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>28614</v>
+        <v>21461</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="5" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -6902,23 +6902,23 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>8856000</v>
+        <v>6642000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>28753</v>
+        <v>21565</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="5" t="n">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -18593,7 +18593,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -22959,7 +22959,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -23409,7 +23409,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -25335,7 +25335,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -25397,7 +25397,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -25777,7 +25777,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -25904,38 +25904,30 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H392" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I392" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="H392" s="5" t="n">
+        <v>16968000</v>
+      </c>
+      <c r="I392" s="5" t="n">
+        <v>22008</v>
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K392" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L392" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K392" s="5" t="n">
+        <v>16968000</v>
+      </c>
+      <c r="L392" s="5" t="n">
+        <v>22008</v>
       </c>
       <c r="M392" s="3" t="inlineStr">
         <is>
@@ -25944,7 +25936,7 @@
       </c>
       <c r="N392" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -74399,7 +74391,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -74409,7 +74401,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -75104,12 +75096,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>G | 306呎 (1房)
-$876万
-$28,614/呎
-(在售)</t>
+$657万
+$21,461/呎
+(26年-10月-10日)</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -75350,12 +75342,12 @@
 (26年-09月-24日)</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K12" s="24" t="inlineStr">
         <is>
           <t>K | 308呎 (1房)
-$886万
-$28,753/呎
-(在售)</t>
+$664万
+$21,565/呎
+(26年-10月-11日)</t>
         </is>
       </c>
       <c r="L12" s="23" t="inlineStr">
@@ -75926,7 +75918,7 @@
           <t>M | 481呎 (2房)
 $1096万
 $22,796/呎
-(26年-09月-20日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
@@ -76259,7 +76251,7 @@
           <t>M | 481呎 (2房)
 $1080万
 $22,453/呎
-(26年-09月-26日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="N20" s="23" t="inlineStr">
@@ -76473,7 +76465,7 @@
           <t>L | 430呎 (2房)
 $935万
 $21,751/呎
-(26年-09月-23日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="M22" s="24" t="inlineStr">
@@ -76774,7 +76766,7 @@
           <t>G | 306呎 (1房)
 $589万
 $19,235/呎
-(26年-09月-10日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="I25" s="24" t="inlineStr">
@@ -76917,7 +76909,7 @@
           <t>L | 430呎 (2房)
 $916万
 $21,309/呎
-(26年-09月-19日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="M26" s="24" t="inlineStr">
@@ -77115,7 +77107,7 @@
           <t>H | 305呎 (1房)
 $580万
 $19,010/呎
-(26年-09月-28日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="J28" s="24" t="inlineStr">
@@ -77440,7 +77432,7 @@
           <t>G | 306呎 (1房)
 $569万
 $18,588/呎
-(26年-09月-10日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="I31" s="24" t="inlineStr">
@@ -77599,7 +77591,7 @@
           <t>N | 288呎 (1房)
 $596万
 $20,677/呎
-(26年-10月-03日)</t>
+(26年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -77720,12 +77712,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>A | 771呎 (3房)
-招标单位
--
-(在售)</t>
+$1697万
+$22,008/呎
+(26年-10月-10日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -77741,7 +77733,7 @@
           <t>C | 498呎 (2房)
 $997万
 $20,016/呎
-(26年-09月-21日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -77789,7 +77781,7 @@
           <t>J | 305呎 (1房)
 $564万
 $18,485/呎
-(26年-09月-19日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="K34" s="24" t="inlineStr">
@@ -77797,7 +77789,7 @@
           <t>K | 308呎 (1房)
 $578万
 $18,776/呎
-(26年-09月-21日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="L34" s="23" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -15120,23 +15120,23 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
-        <v>8480000</v>
+        <v>6360000</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>29444</v>
+        <v>22083</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K224" s="5" t="n">
@@ -15147,7 +15147,7 @@
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
@@ -20361,7 +20361,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -74391,7 +74391,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -74401,7 +74401,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>170</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -76476,12 +76476,12 @@
 (26年-09月-24日)</t>
         </is>
       </c>
-      <c r="N22" s="23" t="inlineStr">
+      <c r="N22" s="24" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
-$848万
-$29,444/呎
-(在售)</t>
+$636万
+$22,083/呎
+(26年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -77099,7 +77099,7 @@
           <t>G | 306呎 (1房)
 $580万
 $18,948/呎
-(26年-09月-28日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="I28" s="24" t="inlineStr">
@@ -77115,7 +77115,7 @@
           <t>J | 305呎 (1房)
 $584万
 $19,141/呎
-(26年-09月-28日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="K28" s="24" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -25149,7 +25149,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -73783,7 +73783,7 @@
       </c>
       <c r="G1115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H1115" s="5" t="n">
@@ -73969,7 +73969,7 @@
       </c>
       <c r="G1118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H1118" s="5" t="n">
@@ -77765,7 +77765,7 @@
           <t>G | 306呎 (1房)
 $560万
 $18,301/呎
-(26年-09月-20日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="I34" s="24" t="inlineStr">
@@ -77813,7 +77813,7 @@
           <t>N | 288呎 (1房)
 $591万
 $20,507/呎
-(26年-09月-28日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -84411,7 +84411,7 @@
           <t>H | 306呎 (1房)
 $580万
 $18,954/呎
-(26年-09月-23日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="J32" s="24" t="inlineStr">
@@ -84435,7 +84435,7 @@
           <t>L | 307呎 (1房)
 $568万
 $18,502/呎
-(26年-09月-22日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="M32" s="24" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -7026,34 +7026,34 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
-        <v>8585000</v>
+        <v>6439000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>28148</v>
+        <v>21111</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="5" t="n">
-        <v>6438750</v>
+        <v>6439000</v>
       </c>
       <c r="L99" s="5" t="n">
         <v>21111</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
@@ -11768,34 +11768,34 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
-        <v>8737000</v>
+        <v>6553000</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>30337</v>
+        <v>22753</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K172" s="5" t="n">
-        <v>6552750</v>
+        <v>6553000</v>
       </c>
       <c r="L172" s="5" t="n">
         <v>22753</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N172" s="3" t="inlineStr">
@@ -12404,38 +12404,30 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H182" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I182" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>11089000</v>
+      </c>
+      <c r="I182" s="5" t="n">
+        <v>22267</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K182" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L182" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K182" s="5" t="n">
+        <v>11089000</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>22267</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
@@ -12444,7 +12436,7 @@
       </c>
       <c r="N182" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12676,34 +12668,34 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
-        <v>14470000</v>
+        <v>10853000</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>30083</v>
+        <v>22563</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>10852500</v>
+        <v>10853000</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>22562</v>
+        <v>22563</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N186" s="3" t="inlineStr">
@@ -12805,7 +12797,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12867,7 +12859,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12929,7 +12921,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12991,7 +12983,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -13053,7 +13045,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -13460,34 +13452,34 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>8633000</v>
+        <v>6475000</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>29976</v>
+        <v>22483</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>6474750</v>
+        <v>6475000</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>22482</v>
+        <v>22483</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N198" s="3" t="inlineStr">
@@ -13584,34 +13576,34 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
-        <v>12657000</v>
+        <v>9493000</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>29435</v>
+        <v>22077</v>
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K200" s="5" t="n">
-        <v>9492750</v>
+        <v>9493000</v>
       </c>
       <c r="L200" s="5" t="n">
-        <v>22076</v>
+        <v>22077</v>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N200" s="3" t="inlineStr">
@@ -17424,38 +17416,30 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H260" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I260" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H260" s="5" t="n">
+        <v>10632000</v>
+      </c>
+      <c r="I260" s="5" t="n">
+        <v>21349</v>
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K260" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L260" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K260" s="5" t="n">
+        <v>10632000</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>21349</v>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
@@ -17464,7 +17448,7 @@
       </c>
       <c r="N260" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -20175,7 +20159,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -20299,7 +20283,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -20547,7 +20531,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -21075,7 +21059,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -21447,7 +21431,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -21889,7 +21873,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -22388,38 +22372,30 @@
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H338" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I338" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="H338" s="5" t="n">
+        <v>10198000</v>
+      </c>
+      <c r="I338" s="5" t="n">
+        <v>20478</v>
       </c>
       <c r="J338" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K338" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L338" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K338" s="5" t="n">
+        <v>10198000</v>
+      </c>
+      <c r="L338" s="5" t="n">
+        <v>20478</v>
       </c>
       <c r="M338" s="3" t="inlineStr">
         <is>
@@ -22428,7 +22404,7 @@
       </c>
       <c r="N338" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -22587,7 +22563,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -22711,7 +22687,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -23347,7 +23323,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -24185,7 +24161,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -25206,34 +25182,34 @@
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
-        <v>13333000</v>
+        <v>10000000</v>
       </c>
       <c r="I381" s="5" t="n">
-        <v>27719</v>
+        <v>20790</v>
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K381" s="5" t="n">
-        <v>9999750</v>
+        <v>10000000</v>
       </c>
       <c r="L381" s="5" t="n">
         <v>20790</v>
       </c>
       <c r="M381" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N381" s="3" t="inlineStr">
@@ -64591,7 +64567,7 @@
       </c>
       <c r="G967" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H967" s="5" t="n">
@@ -74391,7 +74367,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -74401,7 +74377,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>179</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -75326,12 +75302,12 @@
 (26年-09月-21日)</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t>H | 305呎 (1房)
-$858万
-$28,148/呎
-(在售)</t>
+$644万
+$21,111/呎
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="J12" s="24" t="inlineStr">
@@ -75952,12 +75928,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-招标单位
--
-(在售)</t>
+$1109万
+$22,267/呎
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -76032,12 +76008,12 @@
 (26年-09月-28日)</t>
         </is>
       </c>
-      <c r="N18" s="23" t="inlineStr">
+      <c r="N18" s="24" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
-$874万
-$30,337/呎
-(在售)</t>
+$655万
+$22,753/呎
+(26年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -76092,7 +76068,7 @@
           <t>F | 427呎 (2房)
 $888万
 $20,801/呎
-(26年-09月-30日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -76100,7 +76076,7 @@
           <t>G | 306呎 (1房)
 $610万
 $19,922/呎
-(26年-09月-28日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="I19" s="24" t="inlineStr">
@@ -76108,7 +76084,7 @@
           <t>H | 305呎 (1房)
 $610万
 $19,987/呎
-(26年-09月-29日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="J19" s="24" t="inlineStr">
@@ -76116,7 +76092,7 @@
           <t>J | 305呎 (1房)
 $614万
 $20,115/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="K19" s="24" t="inlineStr">
@@ -76124,7 +76100,7 @@
           <t>K | 308呎 (1房)
 $629万
 $20,419/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -76135,12 +76111,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M19" s="23" t="inlineStr">
+      <c r="M19" s="24" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
-$1447万
-$30,083/呎
-(在售)</t>
+$1085万
+$22,563/呎
+(26年-10月-19日)</t>
         </is>
       </c>
       <c r="N19" s="22" t="inlineStr">
@@ -76238,12 +76214,12 @@
 (26年-09月-22日)</t>
         </is>
       </c>
-      <c r="L20" s="23" t="inlineStr">
+      <c r="L20" s="24" t="inlineStr">
         <is>
           <t>L | 430呎 (2房)
-$1266万
-$29,435/呎
-(在售)</t>
+$949万
+$22,077/呎
+(26年-10月-25日)</t>
         </is>
       </c>
       <c r="M20" s="24" t="inlineStr">
@@ -76254,12 +76230,12 @@
 (26年-10月-13日)</t>
         </is>
       </c>
-      <c r="N20" s="23" t="inlineStr">
+      <c r="N20" s="24" t="inlineStr">
         <is>
           <t>N | 288呎 (1房)
-$863万
-$29,976/呎
-(在售)</t>
+$648万
+$22,483/呎
+(26年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -76618,12 +76594,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-招标单位
--
-(在售)</t>
+$1063万
+$21,349/呎
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -77091,7 +77067,7 @@
           <t>F | 427呎 (2房)
 $846万
 $19,803/呎
-(26年-09月-29日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
@@ -77123,7 +77099,7 @@
           <t>K | 308呎 (1房)
 $599万
 $19,435/呎
-(26年-09月-29日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -77139,7 +77115,7 @@
           <t>M | 481呎 (2房)
 $1032万
 $21,451/呎
-(26年-09月-28日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="N28" s="22" t="inlineStr">
@@ -77194,7 +77170,7 @@
           <t>E | 437呎 (2房)
 $946万
 $21,638/呎
-(26年-10月-02日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
@@ -77242,7 +77218,7 @@
           <t>L | 430呎 (2房)
 $897万
 $20,853/呎
-(26年-10月-03日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="M29" s="24" t="inlineStr">
@@ -77284,12 +77260,12 @@
 (26年-09月-28日)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>C | 498呎 (2房)
-招标单位
--
-(在售)</t>
+$1020万
+$20,478/呎
+(26年-10月-24日)</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -77353,7 +77329,7 @@
           <t>L | 430呎 (2房)
 $892万
 $20,756/呎
-(26年-09月-30日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="M30" s="24" t="inlineStr">
@@ -77384,7 +77360,7 @@
           <t>A | 771呎 (3房)
 $1729万
 $22,423/呎
-(26年-10月-07日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -77464,7 +77440,7 @@
           <t>L | 430呎 (2房)
 $888万
 $20,642/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="M31" s="24" t="inlineStr">
@@ -77480,7 +77456,7 @@
           <t>N | 288呎 (1房)
 $600万
 $20,819/呎
-(26年-10月-06日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -77495,7 +77471,7 @@
           <t>A | 771呎 (3房)
 $1718万
 $22,280/呎
-(26年-09月-30日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -77800,12 +77776,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M34" s="23" t="inlineStr">
+      <c r="M34" s="24" t="inlineStr">
         <is>
           <t>M | 481呎 (2房)
-$1333万
-$27,719/呎
-(在售)</t>
+$1000万
+$20,790/呎
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="N34" s="24" t="inlineStr">
@@ -83061,7 +83037,7 @@
           <t>D | 432呎 (2房)
 $989万
 $22,889/呎
-(26年-09月-22日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
